--- a/modules/vas/vas_report_labels.xlsx
+++ b/modules/vas/vas_report_labels.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t xml:space="preserve">question_code</t>
   </si>
@@ -32,7 +32,7 @@
     <t xml:space="preserve">Gender</t>
   </si>
   <si>
-    <t xml:space="preserve">unchanged — the survey text already reads as a label</t>
+    <t xml:space="preserve">unchanged — already reads as a label</t>
   </si>
   <si>
     <t xml:space="preserve">Race</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">Type of area lived in</t>
   </si>
   <si>
-    <t xml:space="preserve">matches reader_label() in the reporting build</t>
+    <t xml:space="preserve">matches the reporting build</t>
   </si>
   <si>
     <t xml:space="preserve">Income</t>
@@ -71,46 +71,127 @@
     <t xml:space="preserve">was: Monthly household income category?</t>
   </si>
   <si>
-    <t xml:space="preserve">IncomeBand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monthly household income (banded)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">the verbatim banded answer — distinct from Income</t>
-  </si>
-  <si>
     <t xml:space="preserve">BillPayer</t>
   </si>
   <si>
     <t xml:space="preserve">Role in paying household bills</t>
   </si>
   <si>
+    <t xml:space="preserve">PrepaidElectricity_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy electricity at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. derived from transactions a month above zero, not from the screener</t>
+  </si>
+  <si>
     <t xml:space="preserve">PPU</t>
   </si>
   <si>
     <t xml:space="preserve">Who have you bought electricity for?</t>
   </si>
   <si>
-    <t xml:space="preserve">was the 12-month screener wording; the base already says who is in it</t>
+    <t xml:space="preserve">2. self / other / none — the base already says who is in it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrepaidElectricity_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepaid electricity — transactions a month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrepaidElectricity_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepaid electricity — spend a month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrepaidElectricity_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepaid electricity — value per transaction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. total — per-buyer average, see note below</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrepaidElectricity_Own_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepaid electricity — transactions a month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. for self</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrepaidElectricity_Own_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepaid electricity — spend a month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. for self</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrepaidElectricity_Own_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepaid electricity — value per transaction (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. for self — per-buyer average</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrepaidElectricity_Oth_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepaid electricity — transactions a month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. for others</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrepaidElectricity_Oth_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepaid electricity — spend a month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10. for others</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrepaidElectricity_Oth_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepaid electricity — value per transaction (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11. for others — per-buyer average</t>
   </si>
   <si>
     <t xml:space="preserve">PPUChannelMain</t>
   </si>
   <si>
-    <t xml:space="preserve">Prepaid electricity — main channel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">was: Where do you buy prepaid electricity most often?</t>
+    <t xml:space="preserve">Where do you buy prepaid electricity most often?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.</t>
   </si>
   <si>
     <t xml:space="preserve">PPUOthChannel</t>
   </si>
   <si>
-    <t xml:space="preserve">Prepaid electricity — other channels used</t>
-  </si>
-  <si>
-    <t xml:space="preserve">was: Where else have you bought prepaid electricity in the last 12 months?</t>
+    <t xml:space="preserve">Where else have you bought prepaid electricity?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13. multi-column</t>
   </si>
 </sst>
 </file>
@@ -446,9 +527,9 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="24.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="46.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="60.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="40.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="54.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="62.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -547,18 +628,18 @@
         <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
         <v>22</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>23</v>
-      </c>
-      <c r="C10" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -592,6 +673,105 @@
       </c>
       <c r="C13" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/modules/vas/vas_report_labels.xlsx
+++ b/modules/vas/vas_report_labels.xlsx
@@ -1,205 +1,212 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/duncan/Dev/Turas/modules/vas/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB585A9E-2039-1F44-B01B-6F13E1A39067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="19620" windowHeight="15220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Labels" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Labels" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
-  <si>
-    <t xml:space="preserve">question_code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">question_text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age</t>
-  </si>
-  <si>
-    <t xml:space="preserve">was: What is your age?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gender</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unchanged — already reads as a label</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Race</t>
-  </si>
-  <si>
-    <t xml:space="preserve">was: Which best describes your ethnic group?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Province</t>
-  </si>
-  <si>
-    <t xml:space="preserve">was: Which province do you currently live in?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Town</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coalesced from the nine per-province questions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AreaType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type of area lived in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">matches the reporting build</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Income</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monthly household income</t>
-  </si>
-  <si>
-    <t xml:space="preserve">was: Monthly household income category?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BillPayer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role in paying household bills</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PrepaidElectricity_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy electricity at all in last 12 months?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. derived from transactions a month above zero, not from the screener</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Who have you bought electricity for?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. self / other / none — the base already says who is in it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PrepaidElectricity_Total_TxnPerMonth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prepaid electricity — transactions a month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PrepaidElectricity_Total_MonthlySpend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prepaid electricity — spend a month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PrepaidElectricity_Total_SpendPerTxn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prepaid electricity — value per transaction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. total — per-buyer average, see note below</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PrepaidElectricity_Own_TxnPerMonth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prepaid electricity — transactions a month (for self)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. for self</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PrepaidElectricity_Own_MonthlySpend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prepaid electricity — spend a month (for self)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7. for self</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PrepaidElectricity_Own_SpendPerTxn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prepaid electricity — value per transaction (for self)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8. for self — per-buyer average</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PrepaidElectricity_Oth_TxnPerMonth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prepaid electricity — transactions a month (for others)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9. for others</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PrepaidElectricity_Oth_MonthlySpend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prepaid electricity — spend a month (for others)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10. for others</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PrepaidElectricity_Oth_SpendPerTxn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prepaid electricity — value per transaction (for others)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11. for others — per-buyer average</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPUChannelMain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Where do you buy prepaid electricity most often?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPUOthChannel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Where else have you bought prepaid electricity?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13. multi-column</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="60">
+  <si>
+    <t>question_code</t>
+  </si>
+  <si>
+    <t>question_text</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>was: What is your age?</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>unchanged — already reads as a label</t>
+  </si>
+  <si>
+    <t>Race</t>
+  </si>
+  <si>
+    <t>was: Which best describes your ethnic group?</t>
+  </si>
+  <si>
+    <t>Province</t>
+  </si>
+  <si>
+    <t>was: Which province do you currently live in?</t>
+  </si>
+  <si>
+    <t>Town</t>
+  </si>
+  <si>
+    <t>coalesced from the nine per-province questions</t>
+  </si>
+  <si>
+    <t>AreaType</t>
+  </si>
+  <si>
+    <t>Type of area lived in</t>
+  </si>
+  <si>
+    <t>matches the reporting build</t>
+  </si>
+  <si>
+    <t>Income</t>
+  </si>
+  <si>
+    <t>Monthly household income</t>
+  </si>
+  <si>
+    <t>was: Monthly household income category?</t>
+  </si>
+  <si>
+    <t>BillPayer</t>
+  </si>
+  <si>
+    <t>Role in paying household bills</t>
+  </si>
+  <si>
+    <t>PrepaidElectricity_Purchased</t>
+  </si>
+  <si>
+    <t>Buy electricity at all in last 12 months?</t>
+  </si>
+  <si>
+    <t>1. derived from transactions a month above zero, not from the screener</t>
+  </si>
+  <si>
+    <t>PPU</t>
+  </si>
+  <si>
+    <t>Who have you bought electricity for?</t>
+  </si>
+  <si>
+    <t>2. self / other / none — the base already says who is in it</t>
+  </si>
+  <si>
+    <t>PrepaidElectricity_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t>3. total</t>
+  </si>
+  <si>
+    <t>PrepaidElectricity_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t>4. total</t>
+  </si>
+  <si>
+    <t>PrepaidElectricity_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t>5. total — per-buyer average, see note below</t>
+  </si>
+  <si>
+    <t>PrepaidElectricity_Own_TxnPerMonth</t>
+  </si>
+  <si>
+    <t>6. for self</t>
+  </si>
+  <si>
+    <t>PrepaidElectricity_Own_MonthlySpend</t>
+  </si>
+  <si>
+    <t>7. for self</t>
+  </si>
+  <si>
+    <t>PrepaidElectricity_Own_SpendPerTxn</t>
+  </si>
+  <si>
+    <t>8. for self — per-buyer average</t>
+  </si>
+  <si>
+    <t>PrepaidElectricity_Oth_TxnPerMonth</t>
+  </si>
+  <si>
+    <t>9. for others</t>
+  </si>
+  <si>
+    <t>PrepaidElectricity_Oth_MonthlySpend</t>
+  </si>
+  <si>
+    <t>10. for others</t>
+  </si>
+  <si>
+    <t>PrepaidElectricity_Oth_SpendPerTxn</t>
+  </si>
+  <si>
+    <t>11. for others — per-buyer average</t>
+  </si>
+  <si>
+    <t>PPUChannelMain</t>
+  </si>
+  <si>
+    <t>Where do you buy prepaid electricity most often?</t>
+  </si>
+  <si>
+    <t>12.</t>
+  </si>
+  <si>
+    <t>PPUOthChannel</t>
+  </si>
+  <si>
+    <t>13. multi-column</t>
+  </si>
+  <si>
+    <t>Prepaid electricity transactions per month (for self)</t>
+  </si>
+  <si>
+    <t>Prepaid electricity spend per month (for self)</t>
+  </si>
+  <si>
+    <t>Prepaid electricity transactions per month (for others)</t>
+  </si>
+  <si>
+    <t>Prepaid electricity spend per month (for others)</t>
+  </si>
+  <si>
+    <t>Where else have you bought prepaid electricity in the past 12 months?</t>
+  </si>
+  <si>
+    <t>Prepaid electricity transactions per month (for everyone)</t>
+  </si>
+  <si>
+    <t>Prepaid electricity spend per month (for everyone)</t>
+  </si>
+  <si>
+    <t>Average Prepaid electricity value per transaction (for everyone)</t>
+  </si>
+  <si>
+    <t>Average Prepaid electricity value per transaction (for self)</t>
+  </si>
+  <si>
+    <t>Average Prepaid electricity value per transaction (for others)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -208,10 +215,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <b/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -242,6 +250,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -523,16 +540,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="40.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="54.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="62.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="40.6640625" customWidth="1"/>
+    <col min="2" max="2" width="54.6640625" customWidth="1"/>
+    <col min="3" max="3" width="62.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -543,7 +560,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -554,7 +571,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -565,7 +582,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -576,7 +593,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -587,7 +604,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -598,7 +615,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -609,7 +626,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -620,7 +637,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -631,7 +648,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -642,7 +659,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -653,129 +670,129 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>27</v>
       </c>
       <c r="B12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" t="s">
         <v>28</v>
       </c>
-      <c r="C12" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s">
         <v>30</v>
       </c>
-      <c r="B13" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>31</v>
       </c>
-      <c r="C13" t="s">
+      <c r="B14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>33</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" t="s">
         <v>34</v>
       </c>
-      <c r="C14" t="s">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
+      <c r="B16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" t="s">
         <v>36</v>
       </c>
-      <c r="B15" t="s">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>37</v>
       </c>
-      <c r="C15" t="s">
+      <c r="B17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>39</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" t="s">
         <v>40</v>
       </c>
-      <c r="C16" t="s">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
+      <c r="B19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" t="s">
         <v>42</v>
       </c>
-      <c r="B17" t="s">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>43</v>
       </c>
-      <c r="C17" t="s">
+      <c r="B20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>45</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B21" t="s">
         <v>46</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C21" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
         <v>48</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" t="s">
         <v>49</v>
-      </c>
-      <c r="C19" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>57</v>
-      </c>
-      <c r="B22" t="s">
-        <v>58</v>
-      </c>
-      <c r="C22" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/modules/vas/vas_report_labels.xlsx
+++ b/modules/vas/vas_report_labels.xlsx
@@ -1,212 +1,172 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/duncan/Dev/Turas/modules/vas/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB585A9E-2039-1F44-B01B-6F13E1A39067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="19620" windowHeight="15220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Labels" sheetId="1" r:id="rId1"/>
+    <sheet name="Labels" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="60">
-  <si>
-    <t>question_code</t>
-  </si>
-  <si>
-    <t>question_text</t>
-  </si>
-  <si>
-    <t>note</t>
-  </si>
-  <si>
-    <t>Age</t>
-  </si>
-  <si>
-    <t>was: What is your age?</t>
-  </si>
-  <si>
-    <t>Gender</t>
-  </si>
-  <si>
-    <t>unchanged — already reads as a label</t>
-  </si>
-  <si>
-    <t>Race</t>
-  </si>
-  <si>
-    <t>was: Which best describes your ethnic group?</t>
-  </si>
-  <si>
-    <t>Province</t>
-  </si>
-  <si>
-    <t>was: Which province do you currently live in?</t>
-  </si>
-  <si>
-    <t>Town</t>
-  </si>
-  <si>
-    <t>coalesced from the nine per-province questions</t>
-  </si>
-  <si>
-    <t>AreaType</t>
-  </si>
-  <si>
-    <t>Type of area lived in</t>
-  </si>
-  <si>
-    <t>matches the reporting build</t>
-  </si>
-  <si>
-    <t>Income</t>
-  </si>
-  <si>
-    <t>Monthly household income</t>
-  </si>
-  <si>
-    <t>was: Monthly household income category?</t>
-  </si>
-  <si>
-    <t>BillPayer</t>
-  </si>
-  <si>
-    <t>Role in paying household bills</t>
-  </si>
-  <si>
-    <t>PrepaidElectricity_Purchased</t>
-  </si>
-  <si>
-    <t>Buy electricity at all in last 12 months?</t>
-  </si>
-  <si>
-    <t>1. derived from transactions a month above zero, not from the screener</t>
-  </si>
-  <si>
-    <t>PPU</t>
-  </si>
-  <si>
-    <t>Who have you bought electricity for?</t>
-  </si>
-  <si>
-    <t>2. self / other / none — the base already says who is in it</t>
-  </si>
-  <si>
-    <t>PrepaidElectricity_Total_TxnPerMonth</t>
-  </si>
-  <si>
-    <t>3. total</t>
-  </si>
-  <si>
-    <t>PrepaidElectricity_Total_MonthlySpend</t>
-  </si>
-  <si>
-    <t>4. total</t>
-  </si>
-  <si>
-    <t>PrepaidElectricity_Total_SpendPerTxn</t>
-  </si>
-  <si>
-    <t>5. total — per-buyer average, see note below</t>
-  </si>
-  <si>
-    <t>PrepaidElectricity_Own_TxnPerMonth</t>
-  </si>
-  <si>
-    <t>6. for self</t>
-  </si>
-  <si>
-    <t>PrepaidElectricity_Own_MonthlySpend</t>
-  </si>
-  <si>
-    <t>7. for self</t>
-  </si>
-  <si>
-    <t>PrepaidElectricity_Own_SpendPerTxn</t>
-  </si>
-  <si>
-    <t>8. for self — per-buyer average</t>
-  </si>
-  <si>
-    <t>PrepaidElectricity_Oth_TxnPerMonth</t>
-  </si>
-  <si>
-    <t>9. for others</t>
-  </si>
-  <si>
-    <t>PrepaidElectricity_Oth_MonthlySpend</t>
-  </si>
-  <si>
-    <t>10. for others</t>
-  </si>
-  <si>
-    <t>PrepaidElectricity_Oth_SpendPerTxn</t>
-  </si>
-  <si>
-    <t>11. for others — per-buyer average</t>
-  </si>
-  <si>
-    <t>PPUChannelMain</t>
-  </si>
-  <si>
-    <t>Where do you buy prepaid electricity most often?</t>
-  </si>
-  <si>
-    <t>12.</t>
-  </si>
-  <si>
-    <t>PPUOthChannel</t>
-  </si>
-  <si>
-    <t>13. multi-column</t>
-  </si>
-  <si>
-    <t>Prepaid electricity transactions per month (for self)</t>
-  </si>
-  <si>
-    <t>Prepaid electricity spend per month (for self)</t>
-  </si>
-  <si>
-    <t>Prepaid electricity transactions per month (for others)</t>
-  </si>
-  <si>
-    <t>Prepaid electricity spend per month (for others)</t>
-  </si>
-  <si>
-    <t>Where else have you bought prepaid electricity in the past 12 months?</t>
-  </si>
-  <si>
-    <t>Prepaid electricity transactions per month (for everyone)</t>
-  </si>
-  <si>
-    <t>Prepaid electricity spend per month (for everyone)</t>
-  </si>
-  <si>
-    <t>Average Prepaid electricity value per transaction (for everyone)</t>
-  </si>
-  <si>
-    <t>Average Prepaid electricity value per transaction (for self)</t>
-  </si>
-  <si>
-    <t>Average Prepaid electricity value per transaction (for others)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+  <si>
+    <t xml:space="preserve">question_code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">question_text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">was: What is your age?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unchanged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Race</t>
+  </si>
+  <si>
+    <t xml:space="preserve">was: Which best describes your ethnic group?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Province</t>
+  </si>
+  <si>
+    <t xml:space="preserve">was: Which province do you currently live in?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Town</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coalesced from the nine per-province questions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AreaType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type of area lived in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">matches the reporting build</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly household income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">was: Monthly household income category?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillPayer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role in paying household bills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrepaidElectricity_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy electricity at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">derived from transactions a month above zero, not from the screener</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who have you bought electricity for?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">self / other / none — the base already says who is in it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPUChannelMain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you buy prepaid electricity most often?</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">PPUOthChannel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where else have you bought prepaid electricity in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">note the code: PPU for electricity, ChannelOther for the other two</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airtime_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy airtime at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airtime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who have you bought airtime for?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AirtimeChannelMain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you buy prepaid airtime most often?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AirtimeChannelOther</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where else have you bought prepaid airtime in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy data at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who have you bought data for?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataChannelMain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you buy prepaid data most often?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataChannelOther</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where else have you bought prepaid data in the past 12 months?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -215,11 +175,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -250,15 +209,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -540,16 +490,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="40.6640625" customWidth="1"/>
-    <col min="2" max="2" width="54.6640625" customWidth="1"/>
-    <col min="3" max="3" width="62.6640625" customWidth="1"/>
+    <col min="1" max="1" width="34.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="62.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="60.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -560,7 +510,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -571,7 +521,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -582,7 +532,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -593,7 +543,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -604,7 +554,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -615,7 +565,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -626,7 +576,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -637,7 +587,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -648,7 +598,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -659,7 +609,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -670,129 +620,118 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12">
       <c r="A12" t="s">
         <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" t="s">
         <v>29</v>
       </c>
-      <c r="B13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" t="s">
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>48</v>
-      </c>
-      <c r="B22" t="s">
-        <v>54</v>
-      </c>
-      <c r="C22" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/modules/vas/vas_report_labels.xlsx
+++ b/modules/vas/vas_report_labels.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
   <si>
     <t xml:space="preserve">question_code</t>
   </si>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Buy electricity at all in last 12 months?</t>
   </si>
   <si>
-    <t xml:space="preserve">derived from transactions a month above zero, not from the screener</t>
+    <t xml:space="preserve">DERIVED from transactions above zero</t>
   </si>
   <si>
     <t xml:space="preserve">PPU</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">Who have you bought electricity for?</t>
   </si>
   <si>
-    <t xml:space="preserve">self / other / none — the base already says who is in it</t>
+    <t xml:space="preserve">ASKED — self / other / none</t>
   </si>
   <si>
     <t xml:space="preserve">PPUChannelMain</t>
@@ -110,9 +110,6 @@
     <t xml:space="preserve">Where else have you bought prepaid electricity in the past 12 months?</t>
   </si>
   <si>
-    <t xml:space="preserve">note the code: PPU for electricity, ChannelOther for the other two</t>
-  </si>
-  <si>
     <t xml:space="preserve">Airtime_Purchased</t>
   </si>
   <si>
@@ -159,6 +156,105 @@
   </si>
   <si>
     <t xml:space="preserve">Where else have you bought prepaid data in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lotto_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy LOTTO at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lotto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Played LOTTO in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASKED yes/no — differs from the derived row on 2 respondents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LottoChannelMain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you buy LOTTO most often?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LottoChannelOther</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where else have you bought LOTTO in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Betting_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy betting vouchers at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bought betting vouchers in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BetChannelMain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you buy betting vouchers most often?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BetChannelOther</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where else have you bought betting vouchers in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BetProviders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Betting providers used</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no equivalent in the other categories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BetProviderMain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main betting provider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DigitalVouchers_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy digital vouchers at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voucher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who have you bought digital vouchers for?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASKED — self / other / none; agrees with the derived row exactly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VoucherChannelMain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you buy digital vouchers most often?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VoucherChannelOther</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where else have you bought digital vouchers in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VoucherType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Types of digital voucher bought</t>
   </si>
 </sst>
 </file>
@@ -494,9 +590,9 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="34.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="62.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="60.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="32.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="66.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="58.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -639,15 +735,15 @@
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" t="s">
         <v>33</v>
-      </c>
-      <c r="B14" t="s">
-        <v>34</v>
       </c>
       <c r="C14" t="s">
         <v>23</v>
@@ -655,10 +751,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" t="s">
         <v>35</v>
-      </c>
-      <c r="B15" t="s">
-        <v>36</v>
       </c>
       <c r="C15" t="s">
         <v>26</v>
@@ -666,10 +762,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" t="s">
         <v>37</v>
-      </c>
-      <c r="B16" t="s">
-        <v>38</v>
       </c>
       <c r="C16" t="s">
         <v>29</v>
@@ -677,21 +773,21 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" t="s">
         <v>39</v>
       </c>
-      <c r="B17" t="s">
-        <v>40</v>
-      </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" t="s">
         <v>41</v>
-      </c>
-      <c r="B18" t="s">
-        <v>42</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
@@ -699,10 +795,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" t="s">
         <v>43</v>
-      </c>
-      <c r="B19" t="s">
-        <v>44</v>
       </c>
       <c r="C19" t="s">
         <v>26</v>
@@ -710,10 +806,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" t="s">
         <v>45</v>
-      </c>
-      <c r="B20" t="s">
-        <v>46</v>
       </c>
       <c r="C20" t="s">
         <v>29</v>
@@ -721,13 +817,178 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" t="s">
         <v>47</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
         <v>48</v>
       </c>
-      <c r="C21" t="s">
-        <v>32</v>
+      <c r="B22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>63</v>
+      </c>
+      <c r="B29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>72</v>
+      </c>
+      <c r="B33" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>75</v>
+      </c>
+      <c r="B34" t="s">
+        <v>76</v>
+      </c>
+      <c r="C34" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>77</v>
+      </c>
+      <c r="B35" t="s">
+        <v>78</v>
+      </c>
+      <c r="C35" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>79</v>
+      </c>
+      <c r="B36" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/modules/vas/vas_report_labels.xlsx
+++ b/modules/vas/vas_report_labels.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="139">
   <si>
     <t xml:space="preserve">question_code</t>
   </si>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">Who have you bought electricity for?</t>
   </si>
   <si>
-    <t xml:space="preserve">ASKED — self / other / none</t>
+    <t xml:space="preserve">ASKED - self / other / none</t>
   </si>
   <si>
     <t xml:space="preserve">PPUChannelMain</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">Played LOTTO in last 12 months?</t>
   </si>
   <si>
-    <t xml:space="preserve">ASKED yes/no — differs from the derived row on 2 respondents</t>
+    <t xml:space="preserve">ASKED yes/no - differs from the derived row on 2 respondents</t>
   </si>
   <si>
     <t xml:space="preserve">LottoChannelMain</t>
@@ -236,7 +236,7 @@
     <t xml:space="preserve">Who have you bought digital vouchers for?</t>
   </si>
   <si>
-    <t xml:space="preserve">ASKED — self / other / none; agrees with the derived row exactly</t>
+    <t xml:space="preserve">ASKED - self / other / none; agrees with the derived row exactly</t>
   </si>
   <si>
     <t xml:space="preserve">VoucherChannelMain</t>
@@ -255,6 +255,180 @@
   </si>
   <si>
     <t xml:space="preserve">Types of digital voucher bought</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DomSend_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Send domestic money transfers at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DomSend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sent a domestic money transfer in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASKED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DomSendChannelMain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you send domestic money transfers from most often?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DomSendChannelOther</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where else have you sent domestic money transfers from in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DomRcv_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receive domestic money transfers at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DomRcv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Received a domestic money transfer in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DomRcvChannelMain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you collect domestic money transfers most often?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DomRcvChannelOther</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where else have you collected domestic money transfers in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IntlSend_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Send international money transfers at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IntlSend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sent money outside South Africa in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IntlSendPlatform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform usually used to send</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IntlSendChannelMain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you pay for international money transfers most often?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IntlSendChannelOther</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where else have you paid for international money transfers in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FlightDomestic_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy domestic flights at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FlightInternational_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy international flights at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who have you bought flight tickets for?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASKED - covers domestic and international together</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FlightChannelMain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you buy flight tickets most often?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FlightChannelOther</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where else have you bought flight tickets in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LongDistanceBus_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy long distance bus tickets at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LDBus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who have you bought long distance bus tickets for?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LDBusChannelMain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you buy long distance bus tickets most often?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LDBusChannelOther</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where else have you bought long distance bus tickets in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ShortDistanceBus_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy short distance bus tickets at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDBus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who have you bought short distance bus tickets for?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDBusChannelMain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you buy short distance bus tickets most often?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDBusChannelOther</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where else have you bought short distance bus tickets in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDBusOwnFormat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ticket format usually bought (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDBusOthBuy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ticket format usually bought (for others)</t>
   </si>
 </sst>
 </file>
@@ -591,7 +765,7 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="32.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="66.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="72.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="58.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
@@ -991,6 +1165,314 @@
         <v>67</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>81</v>
+      </c>
+      <c r="B37" t="s">
+        <v>82</v>
+      </c>
+      <c r="C37" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>83</v>
+      </c>
+      <c r="B38" t="s">
+        <v>84</v>
+      </c>
+      <c r="C38" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" t="s">
+        <v>87</v>
+      </c>
+      <c r="C39" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>88</v>
+      </c>
+      <c r="B40" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>92</v>
+      </c>
+      <c r="B42" t="s">
+        <v>93</v>
+      </c>
+      <c r="C42" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>94</v>
+      </c>
+      <c r="B43" t="s">
+        <v>95</v>
+      </c>
+      <c r="C43" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>96</v>
+      </c>
+      <c r="B44" t="s">
+        <v>97</v>
+      </c>
+      <c r="C44" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>98</v>
+      </c>
+      <c r="B45" t="s">
+        <v>99</v>
+      </c>
+      <c r="C45" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>100</v>
+      </c>
+      <c r="B46" t="s">
+        <v>101</v>
+      </c>
+      <c r="C46" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>102</v>
+      </c>
+      <c r="B47" t="s">
+        <v>103</v>
+      </c>
+      <c r="C47" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>104</v>
+      </c>
+      <c r="B48" t="s">
+        <v>105</v>
+      </c>
+      <c r="C48" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>106</v>
+      </c>
+      <c r="B49" t="s">
+        <v>107</v>
+      </c>
+      <c r="C49" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>108</v>
+      </c>
+      <c r="B50" t="s">
+        <v>109</v>
+      </c>
+      <c r="C50" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>110</v>
+      </c>
+      <c r="B51" t="s">
+        <v>111</v>
+      </c>
+      <c r="C51" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>112</v>
+      </c>
+      <c r="B52" t="s">
+        <v>113</v>
+      </c>
+      <c r="C52" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>115</v>
+      </c>
+      <c r="B53" t="s">
+        <v>116</v>
+      </c>
+      <c r="C53" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>117</v>
+      </c>
+      <c r="B54" t="s">
+        <v>118</v>
+      </c>
+      <c r="C54" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>119</v>
+      </c>
+      <c r="B55" t="s">
+        <v>120</v>
+      </c>
+      <c r="C55" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B56" t="s">
+        <v>122</v>
+      </c>
+      <c r="C56" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>123</v>
+      </c>
+      <c r="B57" t="s">
+        <v>124</v>
+      </c>
+      <c r="C57" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>125</v>
+      </c>
+      <c r="B58" t="s">
+        <v>126</v>
+      </c>
+      <c r="C58" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>127</v>
+      </c>
+      <c r="B59" t="s">
+        <v>128</v>
+      </c>
+      <c r="C59" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>129</v>
+      </c>
+      <c r="B60" t="s">
+        <v>130</v>
+      </c>
+      <c r="C60" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>131</v>
+      </c>
+      <c r="B61" t="s">
+        <v>132</v>
+      </c>
+      <c r="C61" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>133</v>
+      </c>
+      <c r="B62" t="s">
+        <v>134</v>
+      </c>
+      <c r="C62" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>135</v>
+      </c>
+      <c r="B63" t="s">
+        <v>136</v>
+      </c>
+      <c r="C63" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>137</v>
+      </c>
+      <c r="B64" t="s">
+        <v>138</v>
+      </c>
+      <c r="C64" t="s">
+        <v>67</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/modules/vas/vas_report_labels.xlsx
+++ b/modules/vas/vas_report_labels.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="207">
   <si>
     <t xml:space="preserve">question_code</t>
   </si>
@@ -429,6 +429,210 @@
   </si>
   <si>
     <t xml:space="preserve">Ticket format usually bought (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who have you paid bills for?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASKED - self / other / none; covers all 14 bill categories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillChannelMain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you pay bills most often?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillChannelOther</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where else have you paid bills in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTraffic_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pay traffic fines at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillClothing_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pay a clothing/fashion account at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillFurniture_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pay a furniture account at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillEducation_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pay education fees at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillHealth_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pay health bills at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillRetail_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pay a retail credit account at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillOther_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pay other bills at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillDSTV_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pay DSTV / Multichoice at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillMunicipal_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pay a municipal account at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTelkom_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pay Telkom / cellphone at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillInsurance_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pay insurance / funeral at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillInternet_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pay an internet subscription at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillVehicle_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pay a vehicle licence at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTVLicence_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pay a TV licence at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who have you bought event tickets for?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASKED - self / someone else / for a group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Types of event ticket bought</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventChannelMain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you buy event tickets most often?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventChannelOther</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where else have you bought event tickets in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventSportWatch_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy tickets to watch sport at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventSportPlay_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy entry to play sport at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventConcert_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy concert tickets at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventCultural_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy cultural event tickets at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventTheatre_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy theatre tickets at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventOther_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy other event tickets at all in last 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TotalBillSpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total bill payments a month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">was an internal note about spend classes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TotalConsumptionSpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total spend on services a month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">was an internal note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TotalTransferSent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total money sent a month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TotalValueTransacted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total value transacted a month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TotalTxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total transactions a month</t>
   </si>
 </sst>
 </file>
@@ -1473,6 +1677,358 @@
         <v>67</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>139</v>
+      </c>
+      <c r="B65" t="s">
+        <v>140</v>
+      </c>
+      <c r="C65" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>142</v>
+      </c>
+      <c r="B66" t="s">
+        <v>143</v>
+      </c>
+      <c r="C66" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>144</v>
+      </c>
+      <c r="B67" t="s">
+        <v>145</v>
+      </c>
+      <c r="C67" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>146</v>
+      </c>
+      <c r="B68" t="s">
+        <v>147</v>
+      </c>
+      <c r="C68" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>148</v>
+      </c>
+      <c r="B69" t="s">
+        <v>149</v>
+      </c>
+      <c r="C69" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>150</v>
+      </c>
+      <c r="B70" t="s">
+        <v>151</v>
+      </c>
+      <c r="C70" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>152</v>
+      </c>
+      <c r="B71" t="s">
+        <v>153</v>
+      </c>
+      <c r="C71" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>154</v>
+      </c>
+      <c r="B72" t="s">
+        <v>155</v>
+      </c>
+      <c r="C72" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>156</v>
+      </c>
+      <c r="B73" t="s">
+        <v>157</v>
+      </c>
+      <c r="C73" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>158</v>
+      </c>
+      <c r="B74" t="s">
+        <v>159</v>
+      </c>
+      <c r="C74" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>160</v>
+      </c>
+      <c r="B75" t="s">
+        <v>161</v>
+      </c>
+      <c r="C75" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>162</v>
+      </c>
+      <c r="B76" t="s">
+        <v>163</v>
+      </c>
+      <c r="C76" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>164</v>
+      </c>
+      <c r="B77" t="s">
+        <v>165</v>
+      </c>
+      <c r="C77" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>166</v>
+      </c>
+      <c r="B78" t="s">
+        <v>167</v>
+      </c>
+      <c r="C78" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>168</v>
+      </c>
+      <c r="B79" t="s">
+        <v>169</v>
+      </c>
+      <c r="C79" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>170</v>
+      </c>
+      <c r="B80" t="s">
+        <v>171</v>
+      </c>
+      <c r="C80" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>172</v>
+      </c>
+      <c r="B81" t="s">
+        <v>173</v>
+      </c>
+      <c r="C81" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>174</v>
+      </c>
+      <c r="B82" t="s">
+        <v>175</v>
+      </c>
+      <c r="C82" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>177</v>
+      </c>
+      <c r="B83" t="s">
+        <v>178</v>
+      </c>
+      <c r="C83" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>179</v>
+      </c>
+      <c r="B84" t="s">
+        <v>180</v>
+      </c>
+      <c r="C84" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>181</v>
+      </c>
+      <c r="B85" t="s">
+        <v>182</v>
+      </c>
+      <c r="C85" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>183</v>
+      </c>
+      <c r="B86" t="s">
+        <v>184</v>
+      </c>
+      <c r="C86" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>185</v>
+      </c>
+      <c r="B87" t="s">
+        <v>186</v>
+      </c>
+      <c r="C87" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>187</v>
+      </c>
+      <c r="B88" t="s">
+        <v>188</v>
+      </c>
+      <c r="C88" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>189</v>
+      </c>
+      <c r="B89" t="s">
+        <v>190</v>
+      </c>
+      <c r="C89" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>191</v>
+      </c>
+      <c r="B90" t="s">
+        <v>192</v>
+      </c>
+      <c r="C90" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>193</v>
+      </c>
+      <c r="B91" t="s">
+        <v>194</v>
+      </c>
+      <c r="C91" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>195</v>
+      </c>
+      <c r="B92" t="s">
+        <v>196</v>
+      </c>
+      <c r="C92" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>198</v>
+      </c>
+      <c r="B93" t="s">
+        <v>199</v>
+      </c>
+      <c r="C93" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>201</v>
+      </c>
+      <c r="B94" t="s">
+        <v>202</v>
+      </c>
+      <c r="C94" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>203</v>
+      </c>
+      <c r="B95" t="s">
+        <v>204</v>
+      </c>
+      <c r="C95" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>205</v>
+      </c>
+      <c r="B96" t="s">
+        <v>206</v>
+      </c>
+      <c r="C96" t="s">
+        <v>200</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/modules/vas/vas_report_labels.xlsx
+++ b/modules/vas/vas_report_labels.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="220">
   <si>
     <t xml:space="preserve">question_code</t>
   </si>
@@ -633,6 +633,45 @@
   </si>
   <si>
     <t xml:space="preserve">Total transactions a month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TotalWalletSpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wallet spend a month (money sent and received excluded)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wallet summary block - Duncan, 13 Aug 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TotalWalletTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wallet transactions a month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TotalWalletSpendSelf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wallet spend a month, for self</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TotalWalletTxnSelf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wallet transactions a month, for self</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TotalGamblingSpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gambling spend a month (stakes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TotalGamblingTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gambling transactions a month</t>
   </si>
 </sst>
 </file>
@@ -640,19 +679,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -675,9 +708,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -967,20 +999,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="32.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="72.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="58.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2027,6 +2054,72 @@
       </c>
       <c r="C96" t="s">
         <v>200</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>207</v>
+      </c>
+      <c r="B97" t="s">
+        <v>208</v>
+      </c>
+      <c r="C97" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>210</v>
+      </c>
+      <c r="B98" t="s">
+        <v>211</v>
+      </c>
+      <c r="C98" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>212</v>
+      </c>
+      <c r="B99" t="s">
+        <v>213</v>
+      </c>
+      <c r="C99" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>214</v>
+      </c>
+      <c r="B100" t="s">
+        <v>215</v>
+      </c>
+      <c r="C100" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>216</v>
+      </c>
+      <c r="B101" t="s">
+        <v>217</v>
+      </c>
+      <c r="C101" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>218</v>
+      </c>
+      <c r="B102" t="s">
+        <v>219</v>
+      </c>
+      <c r="C102" t="s">
+        <v>209</v>
       </c>
     </row>
   </sheetData>

--- a/modules/vas/vas_report_labels.xlsx
+++ b/modules/vas/vas_report_labels.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="277">
   <si>
     <t xml:space="preserve">question_code</t>
   </si>
@@ -95,6 +95,15 @@
     <t xml:space="preserve">ASKED - self / other / none</t>
   </si>
   <si>
+    <t xml:space="preserve">PPUChannelEver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you buy prepaid electricity - all channels used, most often or also?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DERIVED from the most-often and where-else questions</t>
+  </si>
+  <si>
     <t xml:space="preserve">PPUChannelMain</t>
   </si>
   <si>
@@ -104,6 +113,12 @@
     <t xml:space="preserve"/>
   </si>
   <si>
+    <t xml:space="preserve">PPUChannelAlso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where else do you buy prepaid electricity - apart from the channel used most often?</t>
+  </si>
+  <si>
     <t xml:space="preserve">PPUOthChannel</t>
   </si>
   <si>
@@ -122,12 +137,24 @@
     <t xml:space="preserve">Who have you bought airtime for?</t>
   </si>
   <si>
+    <t xml:space="preserve">AirtimeChannelEver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you buy prepaid airtime - all channels used, most often or also?</t>
+  </si>
+  <si>
     <t xml:space="preserve">AirtimeChannelMain</t>
   </si>
   <si>
     <t xml:space="preserve">Where do you buy prepaid airtime most often?</t>
   </si>
   <si>
+    <t xml:space="preserve">AirtimeChannelAlso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where else do you buy prepaid airtime - apart from the channel used most often?</t>
+  </si>
+  <si>
     <t xml:space="preserve">AirtimeChannelOther</t>
   </si>
   <si>
@@ -146,12 +173,24 @@
     <t xml:space="preserve">Who have you bought data for?</t>
   </si>
   <si>
+    <t xml:space="preserve">DataChannelEver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you buy prepaid data - all channels used, most often or also?</t>
+  </si>
+  <si>
     <t xml:space="preserve">DataChannelMain</t>
   </si>
   <si>
     <t xml:space="preserve">Where do you buy prepaid data most often?</t>
   </si>
   <si>
+    <t xml:space="preserve">DataChannelAlso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where else do you buy prepaid data - apart from the channel used most often?</t>
+  </si>
+  <si>
     <t xml:space="preserve">DataChannelOther</t>
   </si>
   <si>
@@ -173,12 +212,24 @@
     <t xml:space="preserve">ASKED yes/no - differs from the derived row on 2 respondents</t>
   </si>
   <si>
+    <t xml:space="preserve">LottoChannelEver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you buy LOTTO - all channels used, most often or also?</t>
+  </si>
+  <si>
     <t xml:space="preserve">LottoChannelMain</t>
   </si>
   <si>
     <t xml:space="preserve">Where do you buy LOTTO most often?</t>
   </si>
   <si>
+    <t xml:space="preserve">LottoChannelAlso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where else do you buy LOTTO - apart from the channel used most often?</t>
+  </si>
+  <si>
     <t xml:space="preserve">LottoChannelOther</t>
   </si>
   <si>
@@ -197,12 +248,24 @@
     <t xml:space="preserve">Bought betting vouchers in last 12 months?</t>
   </si>
   <si>
+    <t xml:space="preserve">BetChannelEver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you buy betting vouchers - all channels used, most often or also?</t>
+  </si>
+  <si>
     <t xml:space="preserve">BetChannelMain</t>
   </si>
   <si>
     <t xml:space="preserve">Where do you buy betting vouchers most often?</t>
   </si>
   <si>
+    <t xml:space="preserve">BetChannelAlso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where else do you buy betting vouchers - apart from the channel used most often?</t>
+  </si>
+  <si>
     <t xml:space="preserve">BetChannelOther</t>
   </si>
   <si>
@@ -239,12 +302,24 @@
     <t xml:space="preserve">ASKED - self / other / none; agrees with the derived row exactly</t>
   </si>
   <si>
+    <t xml:space="preserve">VoucherChannelEver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you buy digital vouchers - all channels used, most often or also?</t>
+  </si>
+  <si>
     <t xml:space="preserve">VoucherChannelMain</t>
   </si>
   <si>
     <t xml:space="preserve">Where do you buy digital vouchers most often?</t>
   </si>
   <si>
+    <t xml:space="preserve">VoucherChannelAlso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where else do you buy digital vouchers - apart from the channel used most often?</t>
+  </si>
+  <si>
     <t xml:space="preserve">VoucherChannelOther</t>
   </si>
   <si>
@@ -272,12 +347,24 @@
     <t xml:space="preserve">ASKED</t>
   </si>
   <si>
+    <t xml:space="preserve">DomSendChannelEver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you send domestic money transfers from - all channels used, most often or also?</t>
+  </si>
+  <si>
     <t xml:space="preserve">DomSendChannelMain</t>
   </si>
   <si>
     <t xml:space="preserve">Where do you send domestic money transfers from most often?</t>
   </si>
   <si>
+    <t xml:space="preserve">DomSendChannelAlso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where else do you send domestic money transfers from - apart from the channel used most often?</t>
+  </si>
+  <si>
     <t xml:space="preserve">DomSendChannelOther</t>
   </si>
   <si>
@@ -296,12 +383,24 @@
     <t xml:space="preserve">Received a domestic money transfer in last 12 months?</t>
   </si>
   <si>
+    <t xml:space="preserve">DomRcvChannelEver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you collect domestic money transfers - all channels used, most often or also?</t>
+  </si>
+  <si>
     <t xml:space="preserve">DomRcvChannelMain</t>
   </si>
   <si>
     <t xml:space="preserve">Where do you collect domestic money transfers most often?</t>
   </si>
   <si>
+    <t xml:space="preserve">DomRcvChannelAlso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where else do you collect domestic money transfers - apart from the channel used most often?</t>
+  </si>
+  <si>
     <t xml:space="preserve">DomRcvChannelOther</t>
   </si>
   <si>
@@ -326,12 +425,24 @@
     <t xml:space="preserve">Platform usually used to send</t>
   </si>
   <si>
+    <t xml:space="preserve">IntlSendChannelEver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you pay for international money transfers - all channels used, most often or also?</t>
+  </si>
+  <si>
     <t xml:space="preserve">IntlSendChannelMain</t>
   </si>
   <si>
     <t xml:space="preserve">Where do you pay for international money transfers most often?</t>
   </si>
   <si>
+    <t xml:space="preserve">IntlSendChannelAlso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where else do you pay for international money transfers - apart from the channel used most often?</t>
+  </si>
+  <si>
     <t xml:space="preserve">IntlSendChannelOther</t>
   </si>
   <si>
@@ -359,12 +470,24 @@
     <t xml:space="preserve">ASKED - covers domestic and international together</t>
   </si>
   <si>
+    <t xml:space="preserve">FlightChannelEver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you buy flight tickets - all channels used, most often or also?</t>
+  </si>
+  <si>
     <t xml:space="preserve">FlightChannelMain</t>
   </si>
   <si>
     <t xml:space="preserve">Where do you buy flight tickets most often?</t>
   </si>
   <si>
+    <t xml:space="preserve">FlightChannelAlso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where else do you buy flight tickets - apart from the channel used most often?</t>
+  </si>
+  <si>
     <t xml:space="preserve">FlightChannelOther</t>
   </si>
   <si>
@@ -383,12 +506,24 @@
     <t xml:space="preserve">Who have you bought long distance bus tickets for?</t>
   </si>
   <si>
+    <t xml:space="preserve">LDBusChannelEver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you buy long distance bus tickets - all channels used, most often or also?</t>
+  </si>
+  <si>
     <t xml:space="preserve">LDBusChannelMain</t>
   </si>
   <si>
     <t xml:space="preserve">Where do you buy long distance bus tickets most often?</t>
   </si>
   <si>
+    <t xml:space="preserve">LDBusChannelAlso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where else do you buy long distance bus tickets - apart from the channel used most often?</t>
+  </si>
+  <si>
     <t xml:space="preserve">LDBusChannelOther</t>
   </si>
   <si>
@@ -407,12 +542,24 @@
     <t xml:space="preserve">Who have you bought short distance bus tickets for?</t>
   </si>
   <si>
+    <t xml:space="preserve">SDBusChannelEver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you buy short distance bus tickets - all channels used, most often or also?</t>
+  </si>
+  <si>
     <t xml:space="preserve">SDBusChannelMain</t>
   </si>
   <si>
     <t xml:space="preserve">Where do you buy short distance bus tickets most often?</t>
   </si>
   <si>
+    <t xml:space="preserve">SDBusChannelAlso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where else do you buy short distance bus tickets - apart from the channel used most often?</t>
+  </si>
+  <si>
     <t xml:space="preserve">SDBusChannelOther</t>
   </si>
   <si>
@@ -440,12 +587,24 @@
     <t xml:space="preserve">ASKED - self / other / none; covers all 14 bill categories</t>
   </si>
   <si>
+    <t xml:space="preserve">BillChannelEver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you pay bills - all channels used, most often or also?</t>
+  </si>
+  <si>
     <t xml:space="preserve">BillChannelMain</t>
   </si>
   <si>
     <t xml:space="preserve">Where do you pay bills most often?</t>
   </si>
   <si>
+    <t xml:space="preserve">BillChannelAlso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where else do you pay bills - apart from the channel used most often?</t>
+  </si>
+  <si>
     <t xml:space="preserve">BillChannelOther</t>
   </si>
   <si>
@@ -551,10 +710,22 @@
     <t xml:space="preserve">Types of event ticket bought</t>
   </si>
   <si>
+    <t xml:space="preserve">EventChannelEver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you buy event tickets - all channels used, most often or also?</t>
+  </si>
+  <si>
     <t xml:space="preserve">EventChannelMain</t>
   </si>
   <si>
     <t xml:space="preserve">Where do you buy event tickets most often?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventChannelAlso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where else do you buy event tickets - apart from the channel used most often?</t>
   </si>
   <si>
     <t xml:space="preserve">EventChannelOther</t>
@@ -679,13 +850,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -708,8 +885,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -999,15 +1177,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="32.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="72.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="58.71" hidden="0" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1140,81 +1323,81 @@
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s">
         <v>29</v>
@@ -1222,21 +1405,21 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
         <v>23</v>
@@ -1244,13 +1427,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B23" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24">
@@ -1272,7 +1455,7 @@
         <v>56</v>
       </c>
       <c r="C25" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26">
@@ -1283,7 +1466,7 @@
         <v>58</v>
       </c>
       <c r="C26" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27">
@@ -1294,7 +1477,7 @@
         <v>60</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28">
@@ -1305,7 +1488,7 @@
         <v>62</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29">
@@ -1316,18 +1499,18 @@
         <v>64</v>
       </c>
       <c r="C29" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C30" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31">
@@ -1338,7 +1521,7 @@
         <v>69</v>
       </c>
       <c r="C31" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32">
@@ -1349,7 +1532,7 @@
         <v>71</v>
       </c>
       <c r="C32" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33">
@@ -1360,117 +1543,117 @@
         <v>73</v>
       </c>
       <c r="C33" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
+        <v>74</v>
+      </c>
+      <c r="B34" t="s">
         <v>75</v>
       </c>
-      <c r="B34" t="s">
-        <v>76</v>
-      </c>
       <c r="C34" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>76</v>
+      </c>
+      <c r="B35" t="s">
         <v>77</v>
       </c>
-      <c r="B35" t="s">
-        <v>78</v>
-      </c>
       <c r="C35" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>78</v>
+      </c>
+      <c r="B36" t="s">
         <v>79</v>
       </c>
-      <c r="B36" t="s">
-        <v>80</v>
-      </c>
       <c r="C36" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
+        <v>80</v>
+      </c>
+      <c r="B37" t="s">
         <v>81</v>
       </c>
-      <c r="B37" t="s">
-        <v>82</v>
-      </c>
       <c r="C37" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>82</v>
+      </c>
+      <c r="B38" t="s">
         <v>83</v>
       </c>
-      <c r="B38" t="s">
-        <v>84</v>
-      </c>
       <c r="C38" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B39" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C39" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>86</v>
+      </c>
+      <c r="B40" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" t="s">
         <v>88</v>
-      </c>
-      <c r="B40" t="s">
-        <v>89</v>
-      </c>
-      <c r="C40" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>89</v>
+      </c>
+      <c r="B41" t="s">
         <v>90</v>
       </c>
-      <c r="B41" t="s">
-        <v>91</v>
-      </c>
       <c r="C41" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>91</v>
+      </c>
+      <c r="B42" t="s">
         <v>92</v>
       </c>
-      <c r="B42" t="s">
-        <v>93</v>
-      </c>
       <c r="C42" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
+        <v>93</v>
+      </c>
+      <c r="B43" t="s">
         <v>94</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>95</v>
-      </c>
-      <c r="C43" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="44">
@@ -1492,7 +1675,7 @@
         <v>99</v>
       </c>
       <c r="C45" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46">
@@ -1503,7 +1686,7 @@
         <v>101</v>
       </c>
       <c r="C46" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47">
@@ -1514,7 +1697,7 @@
         <v>103</v>
       </c>
       <c r="C47" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48">
@@ -1525,7 +1708,7 @@
         <v>105</v>
       </c>
       <c r="C48" t="s">
-        <v>29</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49">
@@ -1536,7 +1719,7 @@
         <v>107</v>
       </c>
       <c r="C49" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50">
@@ -1547,29 +1730,29 @@
         <v>109</v>
       </c>
       <c r="C50" t="s">
-        <v>23</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B51" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C51" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B52" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C52" t="s">
-        <v>114</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53">
@@ -1591,7 +1774,7 @@
         <v>118</v>
       </c>
       <c r="C54" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55">
@@ -1613,7 +1796,7 @@
         <v>122</v>
       </c>
       <c r="C56" t="s">
-        <v>26</v>
+        <v>110</v>
       </c>
     </row>
     <row r="57">
@@ -1635,7 +1818,7 @@
         <v>126</v>
       </c>
       <c r="C58" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="59">
@@ -1646,7 +1829,7 @@
         <v>128</v>
       </c>
       <c r="C59" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="60">
@@ -1657,7 +1840,7 @@
         <v>130</v>
       </c>
       <c r="C60" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61">
@@ -1668,7 +1851,7 @@
         <v>132</v>
       </c>
       <c r="C61" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="62">
@@ -1679,7 +1862,7 @@
         <v>134</v>
       </c>
       <c r="C62" t="s">
-        <v>29</v>
+        <v>110</v>
       </c>
     </row>
     <row r="63">
@@ -1690,7 +1873,7 @@
         <v>136</v>
       </c>
       <c r="C63" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
     </row>
     <row r="64">
@@ -1701,7 +1884,7 @@
         <v>138</v>
       </c>
       <c r="C64" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
     </row>
     <row r="65">
@@ -1712,15 +1895,15 @@
         <v>140</v>
       </c>
       <c r="C65" t="s">
-        <v>141</v>
+        <v>32</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
+        <v>141</v>
+      </c>
+      <c r="B66" t="s">
         <v>142</v>
-      </c>
-      <c r="B66" t="s">
-        <v>143</v>
       </c>
       <c r="C66" t="s">
         <v>29</v>
@@ -1728,21 +1911,21 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
+        <v>143</v>
+      </c>
+      <c r="B67" t="s">
         <v>144</v>
       </c>
-      <c r="B67" t="s">
-        <v>145</v>
-      </c>
       <c r="C67" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
+        <v>145</v>
+      </c>
+      <c r="B68" t="s">
         <v>146</v>
-      </c>
-      <c r="B68" t="s">
-        <v>147</v>
       </c>
       <c r="C68" t="s">
         <v>23</v>
@@ -1750,10 +1933,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
+        <v>147</v>
+      </c>
+      <c r="B69" t="s">
         <v>148</v>
-      </c>
-      <c r="B69" t="s">
-        <v>149</v>
       </c>
       <c r="C69" t="s">
         <v>23</v>
@@ -1761,13 +1944,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
+        <v>149</v>
+      </c>
+      <c r="B70" t="s">
         <v>150</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
         <v>151</v>
-      </c>
-      <c r="C70" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="71">
@@ -1778,7 +1961,7 @@
         <v>153</v>
       </c>
       <c r="C71" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="72">
@@ -1789,7 +1972,7 @@
         <v>155</v>
       </c>
       <c r="C72" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="73">
@@ -1800,7 +1983,7 @@
         <v>157</v>
       </c>
       <c r="C73" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="74">
@@ -1811,7 +1994,7 @@
         <v>159</v>
       </c>
       <c r="C74" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="75">
@@ -1833,7 +2016,7 @@
         <v>163</v>
       </c>
       <c r="C76" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="77">
@@ -1844,7 +2027,7 @@
         <v>165</v>
       </c>
       <c r="C77" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="78">
@@ -1855,7 +2038,7 @@
         <v>167</v>
       </c>
       <c r="C78" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="79">
@@ -1866,7 +2049,7 @@
         <v>169</v>
       </c>
       <c r="C79" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="80">
@@ -1877,7 +2060,7 @@
         <v>171</v>
       </c>
       <c r="C80" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="81">
@@ -1899,37 +2082,37 @@
         <v>175</v>
       </c>
       <c r="C82" t="s">
-        <v>176</v>
+        <v>26</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
+        <v>176</v>
+      </c>
+      <c r="B83" t="s">
         <v>177</v>
       </c>
-      <c r="B83" t="s">
-        <v>178</v>
-      </c>
       <c r="C83" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
+        <v>178</v>
+      </c>
+      <c r="B84" t="s">
         <v>179</v>
       </c>
-      <c r="B84" t="s">
-        <v>180</v>
-      </c>
       <c r="C84" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
+        <v>180</v>
+      </c>
+      <c r="B85" t="s">
         <v>181</v>
-      </c>
-      <c r="B85" t="s">
-        <v>182</v>
       </c>
       <c r="C85" t="s">
         <v>29</v>
@@ -1937,46 +2120,46 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
+        <v>182</v>
+      </c>
+      <c r="B86" t="s">
         <v>183</v>
       </c>
-      <c r="B86" t="s">
-        <v>184</v>
-      </c>
       <c r="C86" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
+        <v>184</v>
+      </c>
+      <c r="B87" t="s">
         <v>185</v>
       </c>
-      <c r="B87" t="s">
-        <v>186</v>
-      </c>
       <c r="C87" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
+        <v>186</v>
+      </c>
+      <c r="B88" t="s">
         <v>187</v>
       </c>
-      <c r="B88" t="s">
-        <v>188</v>
-      </c>
       <c r="C88" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
+        <v>188</v>
+      </c>
+      <c r="B89" t="s">
         <v>189</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89" t="s">
         <v>190</v>
-      </c>
-      <c r="C89" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="90">
@@ -1987,7 +2170,7 @@
         <v>192</v>
       </c>
       <c r="C90" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="91">
@@ -1998,7 +2181,7 @@
         <v>194</v>
       </c>
       <c r="C91" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="92">
@@ -2009,117 +2192,425 @@
         <v>196</v>
       </c>
       <c r="C92" t="s">
-        <v>197</v>
+        <v>29</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
+        <v>197</v>
+      </c>
+      <c r="B93" t="s">
         <v>198</v>
       </c>
-      <c r="B93" t="s">
-        <v>199</v>
-      </c>
       <c r="C93" t="s">
-        <v>200</v>
+        <v>32</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B94" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C94" t="s">
-        <v>200</v>
+        <v>23</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B95" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C95" t="s">
-        <v>200</v>
+        <v>23</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B96" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C96" t="s">
-        <v>200</v>
+        <v>23</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B97" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C97" t="s">
-        <v>209</v>
+        <v>23</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B98" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C98" t="s">
-        <v>209</v>
+        <v>23</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B99" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C99" t="s">
-        <v>209</v>
+        <v>23</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B100" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C100" t="s">
-        <v>209</v>
+        <v>23</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B101" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C101" t="s">
-        <v>209</v>
+        <v>23</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
+        <v>215</v>
+      </c>
+      <c r="B102" t="s">
+        <v>216</v>
+      </c>
+      <c r="C102" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>217</v>
+      </c>
+      <c r="B103" t="s">
         <v>218</v>
       </c>
-      <c r="B102" t="s">
+      <c r="C103" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
         <v>219</v>
       </c>
-      <c r="C102" t="s">
-        <v>209</v>
+      <c r="B104" t="s">
+        <v>220</v>
+      </c>
+      <c r="C104" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>221</v>
+      </c>
+      <c r="B105" t="s">
+        <v>222</v>
+      </c>
+      <c r="C105" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>223</v>
+      </c>
+      <c r="B106" t="s">
+        <v>224</v>
+      </c>
+      <c r="C106" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>225</v>
+      </c>
+      <c r="B107" t="s">
+        <v>226</v>
+      </c>
+      <c r="C107" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>227</v>
+      </c>
+      <c r="B108" t="s">
+        <v>228</v>
+      </c>
+      <c r="C108" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>230</v>
+      </c>
+      <c r="B109" t="s">
+        <v>231</v>
+      </c>
+      <c r="C109" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>232</v>
+      </c>
+      <c r="B110" t="s">
+        <v>233</v>
+      </c>
+      <c r="C110" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>234</v>
+      </c>
+      <c r="B111" t="s">
+        <v>235</v>
+      </c>
+      <c r="C111" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>236</v>
+      </c>
+      <c r="B112" t="s">
+        <v>237</v>
+      </c>
+      <c r="C112" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>238</v>
+      </c>
+      <c r="B113" t="s">
+        <v>239</v>
+      </c>
+      <c r="C113" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>240</v>
+      </c>
+      <c r="B114" t="s">
+        <v>241</v>
+      </c>
+      <c r="C114" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>242</v>
+      </c>
+      <c r="B115" t="s">
+        <v>243</v>
+      </c>
+      <c r="C115" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>244</v>
+      </c>
+      <c r="B116" t="s">
+        <v>245</v>
+      </c>
+      <c r="C116" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>246</v>
+      </c>
+      <c r="B117" t="s">
+        <v>247</v>
+      </c>
+      <c r="C117" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>248</v>
+      </c>
+      <c r="B118" t="s">
+        <v>249</v>
+      </c>
+      <c r="C118" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>250</v>
+      </c>
+      <c r="B119" t="s">
+        <v>251</v>
+      </c>
+      <c r="C119" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>252</v>
+      </c>
+      <c r="B120" t="s">
+        <v>253</v>
+      </c>
+      <c r="C120" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>255</v>
+      </c>
+      <c r="B121" t="s">
+        <v>256</v>
+      </c>
+      <c r="C121" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>258</v>
+      </c>
+      <c r="B122" t="s">
+        <v>259</v>
+      </c>
+      <c r="C122" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>260</v>
+      </c>
+      <c r="B123" t="s">
+        <v>261</v>
+      </c>
+      <c r="C123" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>262</v>
+      </c>
+      <c r="B124" t="s">
+        <v>263</v>
+      </c>
+      <c r="C124" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>264</v>
+      </c>
+      <c r="B125" t="s">
+        <v>265</v>
+      </c>
+      <c r="C125" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>267</v>
+      </c>
+      <c r="B126" t="s">
+        <v>268</v>
+      </c>
+      <c r="C126" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>269</v>
+      </c>
+      <c r="B127" t="s">
+        <v>270</v>
+      </c>
+      <c r="C127" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>271</v>
+      </c>
+      <c r="B128" t="s">
+        <v>272</v>
+      </c>
+      <c r="C128" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>273</v>
+      </c>
+      <c r="B129" t="s">
+        <v>274</v>
+      </c>
+      <c r="C129" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>275</v>
+      </c>
+      <c r="B130" t="s">
+        <v>276</v>
+      </c>
+      <c r="C130" t="s">
+        <v>266</v>
       </c>
     </row>
   </sheetData>

--- a/modules/vas/vas_report_labels.xlsx
+++ b/modules/vas/vas_report_labels.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="296">
   <si>
     <t xml:space="preserve">question_code</t>
   </si>
@@ -80,55 +80,112 @@
     <t xml:space="preserve">PrepaidElectricity_Purchased</t>
   </si>
   <si>
-    <t xml:space="preserve">Buy electricity at all in last 12 months?</t>
+    <t xml:space="preserve">Did you purchase prepaid electricity in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crosstab planning, 14 Aug 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrepaidElectricity_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How often do you buy prepaid electricity? (all buyers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrepaidElectricity_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much do you spend per month on prepaid electricity? (all buyers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrepaidElectricity_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average prepaid electricity value per transaction (all buyers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrepaidElectricity_Own_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How often do you buy prepaid electricity? (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrepaidElectricity_Own_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much do you spend per month on prepaid electricity? (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrepaidElectricity_Own_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average prepaid electricity value per transaction (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrepaidElectricity_Oth_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How often do you buy prepaid electricity? (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrepaidElectricity_Oth_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much do you spend per month on prepaid electricity? (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrepaidElectricity_Oth_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average prepaid electricity value per transaction (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who have you bought electricity for? (more than one may apply)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASKED - self / other / none</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPUChannelEver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you buy prepaid electricity - all channels used, most often or also?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DERIVED from the most-often and where-else questions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPUChannelMain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you buy prepaid electricity most often?</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">PPUChannelAlso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where else do you buy prepaid electricity - apart from the channel used most often?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPUOthChannel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where else have you bought prepaid electricity in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airtime_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy airtime at all in last 12 months?</t>
   </si>
   <si>
     <t xml:space="preserve">DERIVED from transactions above zero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Who have you bought electricity for?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASKED - self / other / none</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPUChannelEver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Where do you buy prepaid electricity - all channels used, most often or also?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DERIVED from the most-often and where-else questions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPUChannelMain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Where do you buy prepaid electricity most often?</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">PPUChannelAlso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Where else do you buy prepaid electricity - apart from the channel used most often?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPUOthChannel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Where else have you bought prepaid electricity in the past 12 months?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airtime_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy airtime at all in last 12 months?</t>
   </si>
   <si>
     <t xml:space="preserve">Airtime</t>
@@ -1301,59 +1358,59 @@
         <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
         <v>27</v>
       </c>
-      <c r="B12" t="s">
-        <v>28</v>
-      </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
         <v>23</v>
@@ -1361,68 +1418,68 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" t="s">
         <v>47</v>
-      </c>
-      <c r="B21" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" t="s">
         <v>49</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>50</v>
-      </c>
-      <c r="C22" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="23">
@@ -1433,7 +1490,7 @@
         <v>52</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24">
@@ -1444,7 +1501,7 @@
         <v>54</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25">
@@ -1455,51 +1512,51 @@
         <v>56</v>
       </c>
       <c r="C25" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C28" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C29" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30">
@@ -1510,7 +1567,7 @@
         <v>67</v>
       </c>
       <c r="C30" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31">
@@ -1521,7 +1578,7 @@
         <v>69</v>
       </c>
       <c r="C31" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32">
@@ -1532,7 +1589,7 @@
         <v>71</v>
       </c>
       <c r="C32" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33">
@@ -1543,7 +1600,7 @@
         <v>73</v>
       </c>
       <c r="C33" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34">
@@ -1554,7 +1611,7 @@
         <v>75</v>
       </c>
       <c r="C34" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35">
@@ -1565,7 +1622,7 @@
         <v>77</v>
       </c>
       <c r="C35" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36">
@@ -1576,7 +1633,7 @@
         <v>79</v>
       </c>
       <c r="C36" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37">
@@ -1587,7 +1644,7 @@
         <v>81</v>
       </c>
       <c r="C37" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38">
@@ -1598,29 +1655,29 @@
         <v>83</v>
       </c>
       <c r="C38" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B39" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C39" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B40" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C40" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41">
@@ -1631,7 +1688,7 @@
         <v>90</v>
       </c>
       <c r="C41" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42">
@@ -1642,7 +1699,7 @@
         <v>92</v>
       </c>
       <c r="C42" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43">
@@ -1653,73 +1710,73 @@
         <v>94</v>
       </c>
       <c r="C43" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
+        <v>95</v>
+      </c>
+      <c r="B44" t="s">
         <v>96</v>
       </c>
-      <c r="B44" t="s">
-        <v>97</v>
-      </c>
       <c r="C44" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
+        <v>97</v>
+      </c>
+      <c r="B45" t="s">
         <v>98</v>
       </c>
-      <c r="B45" t="s">
-        <v>99</v>
-      </c>
       <c r="C45" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>99</v>
+      </c>
+      <c r="B46" t="s">
         <v>100</v>
       </c>
-      <c r="B46" t="s">
-        <v>101</v>
-      </c>
       <c r="C46" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>101</v>
+      </c>
+      <c r="B47" t="s">
         <v>102</v>
       </c>
-      <c r="B47" t="s">
-        <v>103</v>
-      </c>
       <c r="C47" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
+        <v>103</v>
+      </c>
+      <c r="B48" t="s">
         <v>104</v>
       </c>
-      <c r="B48" t="s">
-        <v>105</v>
-      </c>
       <c r="C48" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>105</v>
+      </c>
+      <c r="B49" t="s">
         <v>106</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>107</v>
-      </c>
-      <c r="C49" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="50">
@@ -1730,29 +1787,29 @@
         <v>109</v>
       </c>
       <c r="C50" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
+        <v>110</v>
+      </c>
+      <c r="B51" t="s">
         <v>111</v>
       </c>
-      <c r="B51" t="s">
-        <v>112</v>
-      </c>
       <c r="C51" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
+        <v>112</v>
+      </c>
+      <c r="B52" t="s">
         <v>113</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>114</v>
-      </c>
-      <c r="C52" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="53">
@@ -1763,7 +1820,7 @@
         <v>116</v>
       </c>
       <c r="C53" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
     </row>
     <row r="54">
@@ -1774,7 +1831,7 @@
         <v>118</v>
       </c>
       <c r="C54" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55">
@@ -1785,7 +1842,7 @@
         <v>120</v>
       </c>
       <c r="C55" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="56">
@@ -1796,7 +1853,7 @@
         <v>122</v>
       </c>
       <c r="C56" t="s">
-        <v>110</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57">
@@ -1807,7 +1864,7 @@
         <v>124</v>
       </c>
       <c r="C57" t="s">
-        <v>29</v>
+        <v>107</v>
       </c>
     </row>
     <row r="58">
@@ -1818,7 +1875,7 @@
         <v>126</v>
       </c>
       <c r="C58" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
     </row>
     <row r="59">
@@ -1829,128 +1886,128 @@
         <v>128</v>
       </c>
       <c r="C59" t="s">
-        <v>29</v>
+        <v>129</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B60" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C60" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B61" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C61" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B62" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C62" t="s">
-        <v>110</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B63" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C63" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B64" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C64" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B65" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C65" t="s">
-        <v>32</v>
+        <v>129</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B66" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C66" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B67" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C67" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B68" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C68" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B69" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C69" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B70" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C70" t="s">
-        <v>151</v>
+        <v>57</v>
       </c>
     </row>
     <row r="71">
@@ -1961,7 +2018,7 @@
         <v>153</v>
       </c>
       <c r="C71" t="s">
-        <v>29</v>
+        <v>129</v>
       </c>
     </row>
     <row r="72">
@@ -1972,7 +2029,7 @@
         <v>155</v>
       </c>
       <c r="C72" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
     </row>
     <row r="73">
@@ -1983,7 +2040,7 @@
         <v>157</v>
       </c>
       <c r="C73" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
     </row>
     <row r="74">
@@ -1994,7 +2051,7 @@
         <v>159</v>
       </c>
       <c r="C74" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="75">
@@ -2005,7 +2062,7 @@
         <v>161</v>
       </c>
       <c r="C75" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="76">
@@ -2016,7 +2073,7 @@
         <v>163</v>
       </c>
       <c r="C76" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
     </row>
     <row r="77">
@@ -2027,7 +2084,7 @@
         <v>165</v>
       </c>
       <c r="C77" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
     </row>
     <row r="78">
@@ -2038,7 +2095,7 @@
         <v>167</v>
       </c>
       <c r="C78" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
     </row>
     <row r="79">
@@ -2049,117 +2106,117 @@
         <v>169</v>
       </c>
       <c r="C79" t="s">
-        <v>29</v>
+        <v>170</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B80" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C80" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B81" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C81" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B82" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C82" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B83" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C83" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B84" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C84" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B85" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C85" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B86" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C86" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B87" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C87" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B88" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C88" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B89" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C89" t="s">
-        <v>190</v>
+        <v>50</v>
       </c>
     </row>
     <row r="90">
@@ -2170,7 +2227,7 @@
         <v>192</v>
       </c>
       <c r="C90" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
     </row>
     <row r="91">
@@ -2181,7 +2238,7 @@
         <v>194</v>
       </c>
       <c r="C91" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="92">
@@ -2192,7 +2249,7 @@
         <v>196</v>
       </c>
       <c r="C92" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
     </row>
     <row r="93">
@@ -2203,7 +2260,7 @@
         <v>198</v>
       </c>
       <c r="C93" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="94">
@@ -2214,7 +2271,7 @@
         <v>200</v>
       </c>
       <c r="C94" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="95">
@@ -2225,7 +2282,7 @@
         <v>202</v>
       </c>
       <c r="C95" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
     </row>
     <row r="96">
@@ -2236,7 +2293,7 @@
         <v>204</v>
       </c>
       <c r="C96" t="s">
-        <v>23</v>
+        <v>107</v>
       </c>
     </row>
     <row r="97">
@@ -2247,7 +2304,7 @@
         <v>206</v>
       </c>
       <c r="C97" t="s">
-        <v>23</v>
+        <v>107</v>
       </c>
     </row>
     <row r="98">
@@ -2258,117 +2315,117 @@
         <v>208</v>
       </c>
       <c r="C98" t="s">
-        <v>23</v>
+        <v>209</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B99" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C99" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B100" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C100" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B101" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C101" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B102" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C102" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B103" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C103" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B104" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C104" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B105" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C105" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B106" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C106" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B107" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C107" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B108" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C108" t="s">
-        <v>229</v>
+        <v>57</v>
       </c>
     </row>
     <row r="109">
@@ -2379,7 +2436,7 @@
         <v>231</v>
       </c>
       <c r="C109" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
     </row>
     <row r="110">
@@ -2390,7 +2447,7 @@
         <v>233</v>
       </c>
       <c r="C110" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
     </row>
     <row r="111">
@@ -2401,7 +2458,7 @@
         <v>235</v>
       </c>
       <c r="C111" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
     </row>
     <row r="112">
@@ -2412,7 +2469,7 @@
         <v>237</v>
       </c>
       <c r="C112" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
     </row>
     <row r="113">
@@ -2423,7 +2480,7 @@
         <v>239</v>
       </c>
       <c r="C113" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
     </row>
     <row r="114">
@@ -2434,7 +2491,7 @@
         <v>241</v>
       </c>
       <c r="C114" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="115">
@@ -2445,7 +2502,7 @@
         <v>243</v>
       </c>
       <c r="C115" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="116">
@@ -2456,7 +2513,7 @@
         <v>245</v>
       </c>
       <c r="C116" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="117">
@@ -2467,40 +2524,40 @@
         <v>247</v>
       </c>
       <c r="C117" t="s">
-        <v>23</v>
+        <v>248</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B118" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C118" t="s">
-        <v>23</v>
+        <v>107</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B119" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C119" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B120" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C120" t="s">
-        <v>254</v>
+        <v>50</v>
       </c>
     </row>
     <row r="121">
@@ -2511,106 +2568,205 @@
         <v>256</v>
       </c>
       <c r="C121" t="s">
-        <v>257</v>
+        <v>47</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
+        <v>257</v>
+      </c>
+      <c r="B122" t="s">
         <v>258</v>
       </c>
-      <c r="B122" t="s">
-        <v>259</v>
-      </c>
       <c r="C122" t="s">
-        <v>257</v>
+        <v>50</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
+        <v>259</v>
+      </c>
+      <c r="B123" t="s">
         <v>260</v>
       </c>
-      <c r="B123" t="s">
-        <v>261</v>
-      </c>
       <c r="C123" t="s">
-        <v>257</v>
+        <v>57</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
+        <v>261</v>
+      </c>
+      <c r="B124" t="s">
         <v>262</v>
       </c>
-      <c r="B124" t="s">
-        <v>263</v>
-      </c>
       <c r="C124" t="s">
-        <v>257</v>
+        <v>57</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
+        <v>263</v>
+      </c>
+      <c r="B125" t="s">
         <v>264</v>
       </c>
-      <c r="B125" t="s">
-        <v>265</v>
-      </c>
       <c r="C125" t="s">
-        <v>266</v>
+        <v>57</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B126" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C126" t="s">
-        <v>266</v>
+        <v>57</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B127" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C127" t="s">
-        <v>266</v>
+        <v>57</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B128" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C128" t="s">
-        <v>266</v>
+        <v>57</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
+        <v>271</v>
+      </c>
+      <c r="B129" t="s">
+        <v>272</v>
+      </c>
+      <c r="C129" t="s">
         <v>273</v>
-      </c>
-      <c r="B129" t="s">
-        <v>274</v>
-      </c>
-      <c r="C129" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
+        <v>274</v>
+      </c>
+      <c r="B130" t="s">
         <v>275</v>
       </c>
-      <c r="B130" t="s">
+      <c r="C130" t="s">
         <v>276</v>
       </c>
-      <c r="C130" t="s">
-        <v>266</v>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>277</v>
+      </c>
+      <c r="B131" t="s">
+        <v>278</v>
+      </c>
+      <c r="C131" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>279</v>
+      </c>
+      <c r="B132" t="s">
+        <v>280</v>
+      </c>
+      <c r="C132" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>281</v>
+      </c>
+      <c r="B133" t="s">
+        <v>282</v>
+      </c>
+      <c r="C133" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>283</v>
+      </c>
+      <c r="B134" t="s">
+        <v>284</v>
+      </c>
+      <c r="C134" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>286</v>
+      </c>
+      <c r="B135" t="s">
+        <v>287</v>
+      </c>
+      <c r="C135" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>288</v>
+      </c>
+      <c r="B136" t="s">
+        <v>289</v>
+      </c>
+      <c r="C136" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>290</v>
+      </c>
+      <c r="B137" t="s">
+        <v>291</v>
+      </c>
+      <c r="C137" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>292</v>
+      </c>
+      <c r="B138" t="s">
+        <v>293</v>
+      </c>
+      <c r="C138" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>294</v>
+      </c>
+      <c r="B139" t="s">
+        <v>295</v>
+      </c>
+      <c r="C139" t="s">
+        <v>285</v>
       </c>
     </row>
   </sheetData>

--- a/modules/vas/vas_report_labels.xlsx
+++ b/modules/vas/vas_report_labels.xlsx
@@ -89,7 +89,7 @@
     <t xml:space="preserve">PrepaidElectricity_Total_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">How often do you buy prepaid electricity? (all buyers)</t>
+    <t xml:space="preserve">Number of Prepaid Electricity transactions per month (all buyers)</t>
   </si>
   <si>
     <t xml:space="preserve">PrepaidElectricity_Total_MonthlySpend</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">PrepaidElectricity_Own_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">How often do you buy prepaid electricity? (for self)</t>
+    <t xml:space="preserve">Number of Prepaid Electricity transactions per month (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">PrepaidElectricity_Own_MonthlySpend</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">PrepaidElectricity_Oth_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">How often do you buy prepaid electricity? (for others)</t>
+    <t xml:space="preserve">Number of Prepaid Electricity transactions per month (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">PrepaidElectricity_Oth_MonthlySpend</t>

--- a/modules/vas/vas_report_labels.xlsx
+++ b/modules/vas/vas_report_labels.xlsx
@@ -89,19 +89,19 @@
     <t xml:space="preserve">PrepaidElectricity_Total_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Prepaid Electricity transactions per month (all buyers)</t>
+    <t xml:space="preserve">Number of Prepaid Electricity transactions per month (all purchases)</t>
   </si>
   <si>
     <t xml:space="preserve">PrepaidElectricity_Total_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">How much do you spend per month on prepaid electricity? (all buyers)</t>
+    <t xml:space="preserve">How much do you spend per month on prepaid electricity? (all purchases)</t>
   </si>
   <si>
     <t xml:space="preserve">PrepaidElectricity_Total_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average prepaid electricity value per transaction (all buyers)</t>
+    <t xml:space="preserve">Average prepaid electricity value per transaction (all purchases)</t>
   </si>
   <si>
     <t xml:space="preserve">PrepaidElectricity_Own_TxnPerMonth</t>

--- a/modules/vas/vas_report_labels.xlsx
+++ b/modules/vas/vas_report_labels.xlsx
@@ -143,7 +143,7 @@
     <t xml:space="preserve">PPU</t>
   </si>
   <si>
-    <t xml:space="preserve">Who have you bought electricity for? (more than one may apply)</t>
+    <t xml:space="preserve">Who have you bought electricity for? (multi-mentions possible)</t>
   </si>
   <si>
     <t xml:space="preserve">ASKED - self / other / none</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">PPUChannelEver</t>
   </si>
   <si>
-    <t xml:space="preserve">Where do you buy prepaid electricity - all channels used, most often or also?</t>
+    <t xml:space="preserve">Where do you buy prepaid electricity - all purchases</t>
   </si>
   <si>
     <t xml:space="preserve">DERIVED from the most-often and where-else questions</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">AirtimeChannelEver</t>
   </si>
   <si>
-    <t xml:space="preserve">Where do you buy prepaid airtime - all channels used, most often or also?</t>
+    <t xml:space="preserve">Where do you buy prepaid airtime - all purchases</t>
   </si>
   <si>
     <t xml:space="preserve">AirtimeChannelMain</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">DataChannelEver</t>
   </si>
   <si>
-    <t xml:space="preserve">Where do you buy prepaid data - all channels used, most often or also?</t>
+    <t xml:space="preserve">Where do you buy prepaid data - all purchases</t>
   </si>
   <si>
     <t xml:space="preserve">DataChannelMain</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">LottoChannelEver</t>
   </si>
   <si>
-    <t xml:space="preserve">Where do you buy LOTTO - all channels used, most often or also?</t>
+    <t xml:space="preserve">Where do you buy LOTTO - all purchases</t>
   </si>
   <si>
     <t xml:space="preserve">LottoChannelMain</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">BetChannelEver</t>
   </si>
   <si>
-    <t xml:space="preserve">Where do you buy betting vouchers - all channels used, most often or also?</t>
+    <t xml:space="preserve">Where do you buy betting vouchers - all purchases</t>
   </si>
   <si>
     <t xml:space="preserve">BetChannelMain</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">VoucherChannelEver</t>
   </si>
   <si>
-    <t xml:space="preserve">Where do you buy digital vouchers - all channels used, most often or also?</t>
+    <t xml:space="preserve">Where do you buy digital vouchers - all purchases</t>
   </si>
   <si>
     <t xml:space="preserve">VoucherChannelMain</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">DomSendChannelEver</t>
   </si>
   <si>
-    <t xml:space="preserve">Where do you send domestic money transfers from - all channels used, most often or also?</t>
+    <t xml:space="preserve">Where do you send domestic money transfers from - all purchases</t>
   </si>
   <si>
     <t xml:space="preserve">DomSendChannelMain</t>
@@ -443,7 +443,7 @@
     <t xml:space="preserve">DomRcvChannelEver</t>
   </si>
   <si>
-    <t xml:space="preserve">Where do you collect domestic money transfers - all channels used, most often or also?</t>
+    <t xml:space="preserve">Where do you collect domestic money transfers - all purchases</t>
   </si>
   <si>
     <t xml:space="preserve">DomRcvChannelMain</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">IntlSendChannelEver</t>
   </si>
   <si>
-    <t xml:space="preserve">Where do you pay for international money transfers - all channels used, most often or also?</t>
+    <t xml:space="preserve">Where do you pay for international money transfers - all purchases</t>
   </si>
   <si>
     <t xml:space="preserve">IntlSendChannelMain</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">FlightChannelEver</t>
   </si>
   <si>
-    <t xml:space="preserve">Where do you buy flight tickets - all channels used, most often or also?</t>
+    <t xml:space="preserve">Where do you buy flight tickets - all purchases</t>
   </si>
   <si>
     <t xml:space="preserve">FlightChannelMain</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">LDBusChannelEver</t>
   </si>
   <si>
-    <t xml:space="preserve">Where do you buy long distance bus tickets - all channels used, most often or also?</t>
+    <t xml:space="preserve">Where do you buy long distance bus tickets - all purchases</t>
   </si>
   <si>
     <t xml:space="preserve">LDBusChannelMain</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">SDBusChannelEver</t>
   </si>
   <si>
-    <t xml:space="preserve">Where do you buy short distance bus tickets - all channels used, most often or also?</t>
+    <t xml:space="preserve">Where do you buy short distance bus tickets - all purchases</t>
   </si>
   <si>
     <t xml:space="preserve">SDBusChannelMain</t>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">BillChannelEver</t>
   </si>
   <si>
-    <t xml:space="preserve">Where do you pay bills - all channels used, most often or also?</t>
+    <t xml:space="preserve">Where do you pay bills - all purchases</t>
   </si>
   <si>
     <t xml:space="preserve">BillChannelMain</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">EventChannelEver</t>
   </si>
   <si>
-    <t xml:space="preserve">Where do you buy event tickets - all channels used, most often or also?</t>
+    <t xml:space="preserve">Where do you buy event tickets - all purchases</t>
   </si>
   <si>
     <t xml:space="preserve">EventChannelMain</t>

--- a/modules/vas/vas_report_labels.xlsx
+++ b/modules/vas/vas_report_labels.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="703">
   <si>
     <t xml:space="preserve">question_code</t>
   </si>
@@ -89,55 +89,1471 @@
     <t xml:space="preserve">PrepaidElectricity_Total_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Prepaid Electricity transactions per month (all purchases)</t>
+    <t xml:space="preserve">Number of Prepaid electricity transactions per month (all purchases)</t>
   </si>
   <si>
     <t xml:space="preserve">PrepaidElectricity_Total_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">How much do you spend per month on prepaid electricity? (all purchases)</t>
+    <t xml:space="preserve">Prepaid electricity spend per month (all purchases)</t>
   </si>
   <si>
     <t xml:space="preserve">PrepaidElectricity_Total_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average prepaid electricity value per transaction (all purchases)</t>
+    <t xml:space="preserve">Average Prepaid electricity value per transaction (all purchases)</t>
   </si>
   <si>
     <t xml:space="preserve">PrepaidElectricity_Own_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Prepaid Electricity transactions per month (for self)</t>
+    <t xml:space="preserve">Number of Prepaid electricity transactions per month (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">PrepaidElectricity_Own_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">How much do you spend per month on prepaid electricity? (for self)</t>
+    <t xml:space="preserve">Prepaid electricity spend per month (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">PrepaidElectricity_Own_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average prepaid electricity value per transaction (for self)</t>
+    <t xml:space="preserve">Average Prepaid electricity value per transaction (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">PrepaidElectricity_Oth_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Prepaid Electricity transactions per month (for others)</t>
+    <t xml:space="preserve">Number of Prepaid electricity transactions per month (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">PrepaidElectricity_Oth_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">How much do you spend per month on prepaid electricity? (for others)</t>
+    <t xml:space="preserve">Prepaid electricity spend per month (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">PrepaidElectricity_Oth_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average prepaid electricity value per transaction (for others)</t>
+    <t xml:space="preserve">Average Prepaid electricity value per transaction (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airtime_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you buy airtime in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airtime_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Prepaid airtime transactions per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airtime_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepaid airtime spend per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airtime_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Prepaid airtime value per transaction (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airtime_Own_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Prepaid airtime transactions per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airtime_Own_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepaid airtime spend per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airtime_Own_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Prepaid airtime value per transaction (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airtime_Oth_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Prepaid airtime transactions per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airtime_Oth_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepaid airtime spend per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airtime_Oth_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Prepaid airtime value per transaction (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you buy data in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Prepaid data transactions per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepaid data spend per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Prepaid data value per transaction (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data_Own_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Prepaid data transactions per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data_Own_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepaid data spend per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data_Own_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Prepaid data value per transaction (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data_Oth_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Prepaid data transactions per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data_Oth_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepaid data spend per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data_Oth_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Prepaid data value per transaction (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DigitalVouchers_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you buy digital vouchers in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DigitalVouchers_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Digital vouchers transactions per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DigitalVouchers_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digital vouchers spend per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DigitalVouchers_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Digital vouchers value per transaction (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DigitalVouchers_Own_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Digital vouchers transactions per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DigitalVouchers_Own_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digital vouchers spend per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DigitalVouchers_Own_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Digital vouchers value per transaction (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DigitalVouchers_Oth_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Digital vouchers transactions per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DigitalVouchers_Oth_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digital vouchers spend per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DigitalVouchers_Oth_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Digital vouchers value per transaction (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ShortDistanceBus_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you buy short distance bus tickets in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ShortDistanceBus_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Short distance bus transactions per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ShortDistanceBus_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Short distance bus spend per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ShortDistanceBus_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Short distance bus value per transaction (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ShortDistanceBus_Own_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Short distance bus transactions per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ShortDistanceBus_Own_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Short distance bus spend per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ShortDistanceBus_Own_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Short distance bus value per transaction (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ShortDistanceBus_Oth_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Short distance bus transactions per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ShortDistanceBus_Oth_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Short distance bus spend per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ShortDistanceBus_Oth_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Short distance bus value per transaction (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTraffic_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you pay traffic fines in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTraffic_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Traffic fines transactions per month (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTraffic_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traffic fines spend per month (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTraffic_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Traffic fines value per transaction (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTraffic_Own_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Traffic fines transactions per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTraffic_Own_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traffic fines spend per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTraffic_Own_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Traffic fines value per transaction (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTraffic_Oth_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Traffic fines transactions per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTraffic_Oth_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traffic fines spend per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTraffic_Oth_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Traffic fines value per transaction (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillClothing_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you pay a clothing/fashion account in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillClothing_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Clothing/fashion transactions per month (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillClothing_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clothing/fashion spend per month (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillClothing_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Clothing/fashion value per transaction (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillClothing_Own_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Clothing/fashion transactions per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillClothing_Own_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clothing/fashion spend per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillClothing_Own_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Clothing/fashion value per transaction (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillClothing_Oth_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Clothing/fashion transactions per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillClothing_Oth_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clothing/fashion spend per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillClothing_Oth_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Clothing/fashion value per transaction (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillFurniture_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you pay a furniture account in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillFurniture_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Furniture transactions per month (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillFurniture_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Furniture spend per month (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillFurniture_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Furniture value per transaction (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillFurniture_Own_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Furniture transactions per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillFurniture_Own_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Furniture spend per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillFurniture_Own_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Furniture value per transaction (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillFurniture_Oth_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Furniture transactions per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillFurniture_Oth_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Furniture spend per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillFurniture_Oth_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Furniture value per transaction (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillEducation_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you pay education fees in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillEducation_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Education transactions per month (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillEducation_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Education spend per month (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillEducation_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Education value per transaction (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillEducation_Own_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Education transactions per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillEducation_Own_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Education spend per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillEducation_Own_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Education value per transaction (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillEducation_Oth_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Education transactions per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillEducation_Oth_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Education spend per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillEducation_Oth_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Education value per transaction (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillHealth_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you pay health bills in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillHealth_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Health transactions per month (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillHealth_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Health spend per month (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillHealth_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Health value per transaction (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillHealth_Own_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Health transactions per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillHealth_Own_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Health spend per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillHealth_Own_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Health value per transaction (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillHealth_Oth_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Health transactions per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillHealth_Oth_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Health spend per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillHealth_Oth_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Health value per transaction (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillRetail_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you pay a retail credit account in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillRetail_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Retail credit transactions per month (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillRetail_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retail credit spend per month (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillRetail_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Retail credit value per transaction (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillRetail_Own_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Retail credit transactions per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillRetail_Own_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retail credit spend per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillRetail_Own_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Retail credit value per transaction (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillRetail_Oth_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Retail credit transactions per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillRetail_Oth_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retail credit spend per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillRetail_Oth_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Retail credit value per transaction (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillOther_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you pay other bills in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillOther_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Other bills transactions per month (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillOther_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other bills spend per month (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillOther_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Other bills value per transaction (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillOther_Own_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Other bills transactions per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillOther_Own_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other bills spend per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillOther_Own_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Other bills value per transaction (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillOther_Oth_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Other bills transactions per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillOther_Oth_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other bills spend per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillOther_Oth_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Other bills value per transaction (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillDSTV_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you pay DSTV / Multichoice in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillDSTV_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of DSTV / Multichoice transactions per month (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillDSTV_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSTV / Multichoice spend per month (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillDSTV_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average DSTV / Multichoice value per transaction (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillDSTV_Own_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of DSTV / Multichoice transactions per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillDSTV_Own_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSTV / Multichoice spend per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillDSTV_Own_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average DSTV / Multichoice value per transaction (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillDSTV_Oth_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of DSTV / Multichoice transactions per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillDSTV_Oth_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSTV / Multichoice spend per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillDSTV_Oth_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average DSTV / Multichoice value per transaction (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillMunicipal_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you pay a municipal account in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillMunicipal_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Municipal account transactions per month (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillMunicipal_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Municipal account spend per month (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillMunicipal_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Municipal account value per transaction (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillMunicipal_Own_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Municipal account transactions per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillMunicipal_Own_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Municipal account spend per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillMunicipal_Own_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Municipal account value per transaction (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillMunicipal_Oth_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Municipal account transactions per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillMunicipal_Oth_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Municipal account spend per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillMunicipal_Oth_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Municipal account value per transaction (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTelkom_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you pay Telkom / cellphone in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTelkom_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Telkom / cellphone transactions per month (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTelkom_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telkom / cellphone spend per month (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTelkom_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Telkom / cellphone value per transaction (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTelkom_Own_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Telkom / cellphone transactions per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTelkom_Own_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telkom / cellphone spend per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTelkom_Own_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Telkom / cellphone value per transaction (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTelkom_Oth_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Telkom / cellphone transactions per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTelkom_Oth_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telkom / cellphone spend per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTelkom_Oth_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Telkom / cellphone value per transaction (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillInsurance_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you pay insurance / funeral in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillInsurance_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Insurance / funeral transactions per month (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillInsurance_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insurance / funeral spend per month (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillInsurance_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Insurance / funeral value per transaction (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillInsurance_Own_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Insurance / funeral transactions per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillInsurance_Own_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insurance / funeral spend per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillInsurance_Own_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Insurance / funeral value per transaction (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillInsurance_Oth_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Insurance / funeral transactions per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillInsurance_Oth_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insurance / funeral spend per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillInsurance_Oth_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Insurance / funeral value per transaction (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillInternet_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you pay an internet subscription in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillInternet_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Internet subscription transactions per month (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillInternet_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internet subscription spend per month (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillInternet_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Internet subscription value per transaction (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillInternet_Own_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Internet subscription transactions per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillInternet_Own_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internet subscription spend per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillInternet_Own_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Internet subscription value per transaction (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillInternet_Oth_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Internet subscription transactions per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillInternet_Oth_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internet subscription spend per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillInternet_Oth_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Internet subscription value per transaction (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillVehicle_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you pay a vehicle licence in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillVehicle_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Vehicle licence transactions per month (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillVehicle_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle licence spend per month (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillVehicle_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Vehicle licence value per transaction (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillVehicle_Own_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Vehicle licence transactions per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillVehicle_Own_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle licence spend per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillVehicle_Own_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Vehicle licence value per transaction (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillVehicle_Oth_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Vehicle licence transactions per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillVehicle_Oth_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle licence spend per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillVehicle_Oth_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Vehicle licence value per transaction (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTVLicence_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you pay a TV licence in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTVLicence_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of TV licence transactions per month (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTVLicence_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TV licence spend per month (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTVLicence_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average TV licence value per transaction (all spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTVLicence_Own_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of TV licence transactions per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTVLicence_Own_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TV licence spend per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTVLicence_Own_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average TV licence value per transaction (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTVLicence_Oth_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of TV licence transactions per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTVLicence_Oth_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TV licence spend per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTVLicence_Oth_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average TV licence value per transaction (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lotto_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you buy LOTTO in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lotto_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of LOTTO transactions per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lotto_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOTTO spend per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lotto_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average LOTTO value per transaction (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Betting_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you buy betting vouchers in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Betting_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Betting vouchers transactions per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Betting_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Betting vouchers spend per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Betting_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Betting vouchers value per transaction (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DomSend_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you send domestic money transfers in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DomSend_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Domestic transfer sent transactions per month (all transfers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DomSend_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domestic transfer sent spend per month (all transfers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DomSend_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Domestic transfer sent value per transaction (all transfers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DomRcv_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you receive domestic money transfers in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DomRcv_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Domestic transfer received transactions per month (all transfers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DomRcv_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domestic transfer received value per month (all transfers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DomRcv_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Domestic transfer received value per transaction (all transfers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IntlSend_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you send international money transfers in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IntlSend_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of International transfer transactions per month (all transfers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IntlSend_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">International transfer spend per month (all transfers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IntlSend_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average International transfer value per transaction (all transfers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventSportWatch_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you buy tickets to watch sport in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventSportWatch_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Sport - watching transactions per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventSportWatch_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sport - watching spend per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventSportWatch_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Sport - watching value per transaction (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventSportPlay_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you buy entry to play sport in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventSportPlay_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Sport - participation transactions per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventSportPlay_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sport - participation spend per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventSportPlay_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Sport - participation value per transaction (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventConcert_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you buy concert tickets in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventConcert_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Concerts transactions per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventConcert_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concerts spend per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventConcert_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Concerts value per transaction (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventCultural_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you buy cultural event tickets in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventCultural_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Cultural events transactions per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventCultural_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cultural events spend per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventCultural_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Cultural events value per transaction (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventTheatre_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you buy theatre tickets in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventTheatre_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Theatre transactions per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventTheatre_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theatre spend per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventTheatre_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Theatre value per transaction (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventOther_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you buy other event tickets in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventOther_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Other events transactions per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventOther_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other events spend per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventOther_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Other events value per transaction (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FlightDomestic_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you buy domestic flights in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FlightDomestic_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Domestic flights transactions per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FlightDomestic_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domestic flights spend per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FlightDomestic_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Domestic flights value per transaction (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FlightInternational_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you buy international flights in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FlightInternational_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of International flights transactions per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FlightInternational_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">International flights spend per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FlightInternational_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average International flights value per transaction (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LongDistanceBus_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you buy long distance bus tickets in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LongDistanceBus_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Long distance bus transactions per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LongDistanceBus_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Long distance bus spend per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LongDistanceBus_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Long distance bus value per transaction (all purchases)</t>
   </si>
   <si>
     <t xml:space="preserve">PPU</t>
@@ -179,19 +1595,10 @@
     <t xml:space="preserve">Where else have you bought prepaid electricity in the past 12 months?</t>
   </si>
   <si>
-    <t xml:space="preserve">Airtime_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy airtime at all in last 12 months?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DERIVED from transactions above zero</t>
-  </si>
-  <si>
     <t xml:space="preserve">Airtime</t>
   </si>
   <si>
-    <t xml:space="preserve">Who have you bought airtime for?</t>
+    <t xml:space="preserve">Who have you bought airtime for? (multi-mentions possible)</t>
   </si>
   <si>
     <t xml:space="preserve">AirtimeChannelEver</t>
@@ -218,16 +1625,10 @@
     <t xml:space="preserve">Where else have you bought prepaid airtime in the past 12 months?</t>
   </si>
   <si>
-    <t xml:space="preserve">Data_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy data at all in last 12 months?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Data</t>
   </si>
   <si>
-    <t xml:space="preserve">Who have you bought data for?</t>
+    <t xml:space="preserve">Who have you bought data for? (multi-mentions possible)</t>
   </si>
   <si>
     <t xml:space="preserve">DataChannelEver</t>
@@ -254,12 +1655,6 @@
     <t xml:space="preserve">Where else have you bought prepaid data in the past 12 months?</t>
   </si>
   <si>
-    <t xml:space="preserve">Lotto_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy LOTTO at all in last 12 months?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lotto</t>
   </si>
   <si>
@@ -293,12 +1688,6 @@
     <t xml:space="preserve">Where else have you bought LOTTO in the past 12 months?</t>
   </si>
   <si>
-    <t xml:space="preserve">Betting_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy betting vouchers at all in last 12 months?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bet</t>
   </si>
   <si>
@@ -344,16 +1733,10 @@
     <t xml:space="preserve">Main betting provider</t>
   </si>
   <si>
-    <t xml:space="preserve">DigitalVouchers_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy digital vouchers at all in last 12 months?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Voucher</t>
   </si>
   <si>
-    <t xml:space="preserve">Who have you bought digital vouchers for?</t>
+    <t xml:space="preserve">Who have you bought digital vouchers for? (multi-mentions possible)</t>
   </si>
   <si>
     <t xml:space="preserve">ASKED - self / other / none; agrees with the derived row exactly</t>
@@ -389,12 +1772,6 @@
     <t xml:space="preserve">Types of digital voucher bought</t>
   </si>
   <si>
-    <t xml:space="preserve">DomSend_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Send domestic money transfers at all in last 12 months?</t>
-  </si>
-  <si>
     <t xml:space="preserve">DomSend</t>
   </si>
   <si>
@@ -407,7 +1784,7 @@
     <t xml:space="preserve">DomSendChannelEver</t>
   </si>
   <si>
-    <t xml:space="preserve">Where do you send domestic money transfers from - all purchases</t>
+    <t xml:space="preserve">Where do you send domestic money transfers from - all transfers</t>
   </si>
   <si>
     <t xml:space="preserve">DomSendChannelMain</t>
@@ -428,12 +1805,6 @@
     <t xml:space="preserve">Where else have you sent domestic money transfers from in the past 12 months?</t>
   </si>
   <si>
-    <t xml:space="preserve">DomRcv_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Receive domestic money transfers at all in last 12 months?</t>
-  </si>
-  <si>
     <t xml:space="preserve">DomRcv</t>
   </si>
   <si>
@@ -443,7 +1814,7 @@
     <t xml:space="preserve">DomRcvChannelEver</t>
   </si>
   <si>
-    <t xml:space="preserve">Where do you collect domestic money transfers - all purchases</t>
+    <t xml:space="preserve">Where do you collect domestic money transfers - all transfers</t>
   </si>
   <si>
     <t xml:space="preserve">DomRcvChannelMain</t>
@@ -464,12 +1835,6 @@
     <t xml:space="preserve">Where else have you collected domestic money transfers in the past 12 months?</t>
   </si>
   <si>
-    <t xml:space="preserve">IntlSend_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Send international money transfers at all in last 12 months?</t>
-  </si>
-  <si>
     <t xml:space="preserve">IntlSend</t>
   </si>
   <si>
@@ -485,7 +1850,7 @@
     <t xml:space="preserve">IntlSendChannelEver</t>
   </si>
   <si>
-    <t xml:space="preserve">Where do you pay for international money transfers - all purchases</t>
+    <t xml:space="preserve">Where do you pay for international money transfers - all transfers</t>
   </si>
   <si>
     <t xml:space="preserve">IntlSendChannelMain</t>
@@ -506,22 +1871,10 @@
     <t xml:space="preserve">Where else have you paid for international money transfers in the past 12 months?</t>
   </si>
   <si>
-    <t xml:space="preserve">FlightDomestic_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy domestic flights at all in last 12 months?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FlightInternational_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy international flights at all in last 12 months?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Flight</t>
   </si>
   <si>
-    <t xml:space="preserve">Who have you bought flight tickets for?</t>
+    <t xml:space="preserve">Who have you bought flight tickets for? (multi-mentions possible)</t>
   </si>
   <si>
     <t xml:space="preserve">ASKED - covers domestic and international together</t>
@@ -551,16 +1904,10 @@
     <t xml:space="preserve">Where else have you bought flight tickets in the past 12 months?</t>
   </si>
   <si>
-    <t xml:space="preserve">LongDistanceBus_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy long distance bus tickets at all in last 12 months?</t>
-  </si>
-  <si>
     <t xml:space="preserve">LDBus</t>
   </si>
   <si>
-    <t xml:space="preserve">Who have you bought long distance bus tickets for?</t>
+    <t xml:space="preserve">Who have you bought long distance bus tickets for? (multi-mentions possible)</t>
   </si>
   <si>
     <t xml:space="preserve">LDBusChannelEver</t>
@@ -587,16 +1934,10 @@
     <t xml:space="preserve">Where else have you bought long distance bus tickets in the past 12 months?</t>
   </si>
   <si>
-    <t xml:space="preserve">ShortDistanceBus_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy short distance bus tickets at all in last 12 months?</t>
-  </si>
-  <si>
     <t xml:space="preserve">SDBus</t>
   </si>
   <si>
-    <t xml:space="preserve">Who have you bought short distance bus tickets for?</t>
+    <t xml:space="preserve">Who have you bought short distance bus tickets for? (multi-mentions possible)</t>
   </si>
   <si>
     <t xml:space="preserve">SDBusChannelEver</t>
@@ -638,7 +1979,7 @@
     <t xml:space="preserve">Bill</t>
   </si>
   <si>
-    <t xml:space="preserve">Who have you paid bills for?</t>
+    <t xml:space="preserve">Who have you paid bills for? (multi-mentions possible)</t>
   </si>
   <si>
     <t xml:space="preserve">ASKED - self / other / none; covers all 14 bill categories</t>
@@ -647,7 +1988,7 @@
     <t xml:space="preserve">BillChannelEver</t>
   </si>
   <si>
-    <t xml:space="preserve">Where do you pay bills - all purchases</t>
+    <t xml:space="preserve">Where do you pay bills - all spend</t>
   </si>
   <si>
     <t xml:space="preserve">BillChannelMain</t>
@@ -668,94 +2009,10 @@
     <t xml:space="preserve">Where else have you paid bills in the past 12 months?</t>
   </si>
   <si>
-    <t xml:space="preserve">BillTraffic_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pay traffic fines at all in last 12 months?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BillClothing_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pay a clothing/fashion account at all in last 12 months?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BillFurniture_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pay a furniture account at all in last 12 months?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BillEducation_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pay education fees at all in last 12 months?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BillHealth_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pay health bills at all in last 12 months?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BillRetail_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pay a retail credit account at all in last 12 months?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BillOther_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pay other bills at all in last 12 months?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BillDSTV_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pay DSTV / Multichoice at all in last 12 months?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BillMunicipal_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pay a municipal account at all in last 12 months?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BillTelkom_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pay Telkom / cellphone at all in last 12 months?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BillInsurance_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pay insurance / funeral at all in last 12 months?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BillInternet_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pay an internet subscription at all in last 12 months?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BillVehicle_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pay a vehicle licence at all in last 12 months?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BillTVLicence_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pay a TV licence at all in last 12 months?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Event</t>
   </si>
   <si>
-    <t xml:space="preserve">Who have you bought event tickets for?</t>
+    <t xml:space="preserve">Who have you bought event tickets for? (multi-mentions possible)</t>
   </si>
   <si>
     <t xml:space="preserve">ASKED - self / someone else / for a group</t>
@@ -789,42 +2046,6 @@
   </si>
   <si>
     <t xml:space="preserve">Where else have you bought event tickets in the past 12 months?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EventSportWatch_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy tickets to watch sport at all in last 12 months?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EventSportPlay_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy entry to play sport at all in last 12 months?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EventConcert_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy concert tickets at all in last 12 months?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EventCultural_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy cultural event tickets at all in last 12 months?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EventTheatre_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy theatre tickets at all in last 12 months?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EventOther_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy other event tickets at all in last 12 months?</t>
   </si>
   <si>
     <t xml:space="preserve">TotalBillSpend</t>
@@ -1457,1316 +2678,3560 @@
         <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" t="s">
         <v>45</v>
       </c>
-      <c r="B21" t="s">
-        <v>46</v>
-      </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B22" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C23" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B24" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C24" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C25" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B27" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C27" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B28" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C28" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B29" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C29" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B30" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C30" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B31" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C31" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C32" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B33" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C33" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B34" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B35" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C35" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B36" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C36" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B37" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C37" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B38" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C38" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B39" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C39" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B40" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C40" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B41" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C41" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B42" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C42" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C43" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B44" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C44" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B45" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C45" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B46" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C46" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B47" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C47" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B48" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C48" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B49" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C49" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B50" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C50" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B51" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C51" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B52" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C52" t="s">
-        <v>114</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B53" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C53" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B54" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C54" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B55" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C55" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B56" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C56" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="B57" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C57" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B58" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C58" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="B59" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C59" t="s">
-        <v>129</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="B60" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C60" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="B61" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C61" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B62" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C62" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="B63" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C63" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B64" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C64" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B65" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C65" t="s">
-        <v>129</v>
+        <v>23</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="B66" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C66" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="B67" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C67" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="B68" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="C68" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="B69" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="C69" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="B70" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="C70" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B71" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C71" t="s">
-        <v>129</v>
+        <v>23</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="B72" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C72" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B73" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="C73" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="B74" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C74" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="B75" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C75" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="B76" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C76" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="B77" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C77" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="B78" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C78" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="B79" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C79" t="s">
-        <v>170</v>
+        <v>23</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="B80" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C80" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="B81" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="C81" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="B82" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="C82" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="B83" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="C83" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="B84" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="C84" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B85" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C85" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="B86" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C86" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B87" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="C87" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="B88" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="C88" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="B89" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="C89" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="B90" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="C90" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="B91" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="C91" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="B92" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C92" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="B93" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C93" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="B94" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="C94" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B95" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="C95" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="B96" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="C96" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="B97" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C97" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="B98" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="C98" t="s">
-        <v>209</v>
+        <v>23</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B99" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="C99" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="B100" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C100" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="B101" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="C101" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="B102" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="C102" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="B103" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="C103" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="B104" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="C104" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="B105" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C105" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="B106" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="C106" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="B107" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="C107" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="B108" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="C108" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B109" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C109" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="B110" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="C110" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="B111" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="C111" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="B112" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="C112" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="B113" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="C113" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="B114" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C114" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="B115" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C115" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="B116" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C116" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="B117" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C117" t="s">
-        <v>248</v>
+        <v>23</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="B118" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="C118" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="B119" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="C119" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="B120" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="C120" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="B121" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="C121" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="B122" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="C122" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="B123" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="C123" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="B124" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="C124" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="B125" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="C125" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="B126" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="C126" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="B127" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="C127" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="B128" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="C128" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="B129" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="C129" t="s">
-        <v>273</v>
+        <v>23</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="B130" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="C130" t="s">
-        <v>276</v>
+        <v>23</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="B131" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="C131" t="s">
-        <v>276</v>
+        <v>23</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="B132" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="C132" t="s">
-        <v>276</v>
+        <v>23</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="B133" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="C133" t="s">
-        <v>276</v>
+        <v>23</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="B134" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="C134" t="s">
-        <v>285</v>
+        <v>23</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="B135" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="C135" t="s">
-        <v>285</v>
+        <v>23</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="B136" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="C136" t="s">
-        <v>285</v>
+        <v>23</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="B137" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="C137" t="s">
-        <v>285</v>
+        <v>23</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="B138" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="C138" t="s">
-        <v>285</v>
+        <v>23</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
+        <v>280</v>
+      </c>
+      <c r="B139" t="s">
+        <v>281</v>
+      </c>
+      <c r="C139" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>282</v>
+      </c>
+      <c r="B140" t="s">
+        <v>283</v>
+      </c>
+      <c r="C140" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>284</v>
+      </c>
+      <c r="B141" t="s">
+        <v>285</v>
+      </c>
+      <c r="C141" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>286</v>
+      </c>
+      <c r="B142" t="s">
+        <v>287</v>
+      </c>
+      <c r="C142" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>288</v>
+      </c>
+      <c r="B143" t="s">
+        <v>289</v>
+      </c>
+      <c r="C143" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>290</v>
+      </c>
+      <c r="B144" t="s">
+        <v>291</v>
+      </c>
+      <c r="C144" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>292</v>
+      </c>
+      <c r="B145" t="s">
+        <v>293</v>
+      </c>
+      <c r="C145" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
         <v>294</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B146" t="s">
         <v>295</v>
       </c>
-      <c r="C139" t="s">
-        <v>285</v>
+      <c r="C146" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>296</v>
+      </c>
+      <c r="B147" t="s">
+        <v>297</v>
+      </c>
+      <c r="C147" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>298</v>
+      </c>
+      <c r="B148" t="s">
+        <v>299</v>
+      </c>
+      <c r="C148" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>300</v>
+      </c>
+      <c r="B149" t="s">
+        <v>301</v>
+      </c>
+      <c r="C149" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>302</v>
+      </c>
+      <c r="B150" t="s">
+        <v>303</v>
+      </c>
+      <c r="C150" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>304</v>
+      </c>
+      <c r="B151" t="s">
+        <v>305</v>
+      </c>
+      <c r="C151" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>306</v>
+      </c>
+      <c r="B152" t="s">
+        <v>307</v>
+      </c>
+      <c r="C152" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>308</v>
+      </c>
+      <c r="B153" t="s">
+        <v>309</v>
+      </c>
+      <c r="C153" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>310</v>
+      </c>
+      <c r="B154" t="s">
+        <v>311</v>
+      </c>
+      <c r="C154" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>312</v>
+      </c>
+      <c r="B155" t="s">
+        <v>313</v>
+      </c>
+      <c r="C155" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>314</v>
+      </c>
+      <c r="B156" t="s">
+        <v>315</v>
+      </c>
+      <c r="C156" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>316</v>
+      </c>
+      <c r="B157" t="s">
+        <v>317</v>
+      </c>
+      <c r="C157" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>318</v>
+      </c>
+      <c r="B158" t="s">
+        <v>319</v>
+      </c>
+      <c r="C158" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>320</v>
+      </c>
+      <c r="B159" t="s">
+        <v>321</v>
+      </c>
+      <c r="C159" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>322</v>
+      </c>
+      <c r="B160" t="s">
+        <v>323</v>
+      </c>
+      <c r="C160" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>324</v>
+      </c>
+      <c r="B161" t="s">
+        <v>325</v>
+      </c>
+      <c r="C161" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>326</v>
+      </c>
+      <c r="B162" t="s">
+        <v>327</v>
+      </c>
+      <c r="C162" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>328</v>
+      </c>
+      <c r="B163" t="s">
+        <v>329</v>
+      </c>
+      <c r="C163" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>330</v>
+      </c>
+      <c r="B164" t="s">
+        <v>331</v>
+      </c>
+      <c r="C164" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>332</v>
+      </c>
+      <c r="B165" t="s">
+        <v>333</v>
+      </c>
+      <c r="C165" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>334</v>
+      </c>
+      <c r="B166" t="s">
+        <v>335</v>
+      </c>
+      <c r="C166" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>336</v>
+      </c>
+      <c r="B167" t="s">
+        <v>337</v>
+      </c>
+      <c r="C167" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>338</v>
+      </c>
+      <c r="B168" t="s">
+        <v>339</v>
+      </c>
+      <c r="C168" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>340</v>
+      </c>
+      <c r="B169" t="s">
+        <v>341</v>
+      </c>
+      <c r="C169" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>342</v>
+      </c>
+      <c r="B170" t="s">
+        <v>343</v>
+      </c>
+      <c r="C170" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>344</v>
+      </c>
+      <c r="B171" t="s">
+        <v>345</v>
+      </c>
+      <c r="C171" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>346</v>
+      </c>
+      <c r="B172" t="s">
+        <v>347</v>
+      </c>
+      <c r="C172" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>348</v>
+      </c>
+      <c r="B173" t="s">
+        <v>349</v>
+      </c>
+      <c r="C173" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>350</v>
+      </c>
+      <c r="B174" t="s">
+        <v>351</v>
+      </c>
+      <c r="C174" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>352</v>
+      </c>
+      <c r="B175" t="s">
+        <v>353</v>
+      </c>
+      <c r="C175" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>354</v>
+      </c>
+      <c r="B176" t="s">
+        <v>355</v>
+      </c>
+      <c r="C176" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>356</v>
+      </c>
+      <c r="B177" t="s">
+        <v>357</v>
+      </c>
+      <c r="C177" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>358</v>
+      </c>
+      <c r="B178" t="s">
+        <v>359</v>
+      </c>
+      <c r="C178" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>360</v>
+      </c>
+      <c r="B179" t="s">
+        <v>361</v>
+      </c>
+      <c r="C179" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>362</v>
+      </c>
+      <c r="B180" t="s">
+        <v>363</v>
+      </c>
+      <c r="C180" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>364</v>
+      </c>
+      <c r="B181" t="s">
+        <v>365</v>
+      </c>
+      <c r="C181" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>366</v>
+      </c>
+      <c r="B182" t="s">
+        <v>367</v>
+      </c>
+      <c r="C182" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>368</v>
+      </c>
+      <c r="B183" t="s">
+        <v>369</v>
+      </c>
+      <c r="C183" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>370</v>
+      </c>
+      <c r="B184" t="s">
+        <v>371</v>
+      </c>
+      <c r="C184" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>372</v>
+      </c>
+      <c r="B185" t="s">
+        <v>373</v>
+      </c>
+      <c r="C185" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>374</v>
+      </c>
+      <c r="B186" t="s">
+        <v>375</v>
+      </c>
+      <c r="C186" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>376</v>
+      </c>
+      <c r="B187" t="s">
+        <v>377</v>
+      </c>
+      <c r="C187" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>378</v>
+      </c>
+      <c r="B188" t="s">
+        <v>379</v>
+      </c>
+      <c r="C188" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>380</v>
+      </c>
+      <c r="B189" t="s">
+        <v>381</v>
+      </c>
+      <c r="C189" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>382</v>
+      </c>
+      <c r="B190" t="s">
+        <v>383</v>
+      </c>
+      <c r="C190" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>384</v>
+      </c>
+      <c r="B191" t="s">
+        <v>385</v>
+      </c>
+      <c r="C191" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>386</v>
+      </c>
+      <c r="B192" t="s">
+        <v>387</v>
+      </c>
+      <c r="C192" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>388</v>
+      </c>
+      <c r="B193" t="s">
+        <v>389</v>
+      </c>
+      <c r="C193" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>390</v>
+      </c>
+      <c r="B194" t="s">
+        <v>391</v>
+      </c>
+      <c r="C194" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>392</v>
+      </c>
+      <c r="B195" t="s">
+        <v>393</v>
+      </c>
+      <c r="C195" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>394</v>
+      </c>
+      <c r="B196" t="s">
+        <v>395</v>
+      </c>
+      <c r="C196" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>396</v>
+      </c>
+      <c r="B197" t="s">
+        <v>397</v>
+      </c>
+      <c r="C197" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>398</v>
+      </c>
+      <c r="B198" t="s">
+        <v>399</v>
+      </c>
+      <c r="C198" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>400</v>
+      </c>
+      <c r="B199" t="s">
+        <v>401</v>
+      </c>
+      <c r="C199" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>402</v>
+      </c>
+      <c r="B200" t="s">
+        <v>403</v>
+      </c>
+      <c r="C200" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>404</v>
+      </c>
+      <c r="B201" t="s">
+        <v>405</v>
+      </c>
+      <c r="C201" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s">
+        <v>406</v>
+      </c>
+      <c r="B202" t="s">
+        <v>407</v>
+      </c>
+      <c r="C202" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s">
+        <v>408</v>
+      </c>
+      <c r="B203" t="s">
+        <v>409</v>
+      </c>
+      <c r="C203" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s">
+        <v>410</v>
+      </c>
+      <c r="B204" t="s">
+        <v>411</v>
+      </c>
+      <c r="C204" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s">
+        <v>412</v>
+      </c>
+      <c r="B205" t="s">
+        <v>413</v>
+      </c>
+      <c r="C205" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s">
+        <v>414</v>
+      </c>
+      <c r="B206" t="s">
+        <v>415</v>
+      </c>
+      <c r="C206" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s">
+        <v>416</v>
+      </c>
+      <c r="B207" t="s">
+        <v>417</v>
+      </c>
+      <c r="C207" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s">
+        <v>418</v>
+      </c>
+      <c r="B208" t="s">
+        <v>419</v>
+      </c>
+      <c r="C208" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s">
+        <v>420</v>
+      </c>
+      <c r="B209" t="s">
+        <v>421</v>
+      </c>
+      <c r="C209" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s">
+        <v>422</v>
+      </c>
+      <c r="B210" t="s">
+        <v>423</v>
+      </c>
+      <c r="C210" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s">
+        <v>424</v>
+      </c>
+      <c r="B211" t="s">
+        <v>425</v>
+      </c>
+      <c r="C211" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s">
+        <v>426</v>
+      </c>
+      <c r="B212" t="s">
+        <v>427</v>
+      </c>
+      <c r="C212" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s">
+        <v>428</v>
+      </c>
+      <c r="B213" t="s">
+        <v>429</v>
+      </c>
+      <c r="C213" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s">
+        <v>430</v>
+      </c>
+      <c r="B214" t="s">
+        <v>431</v>
+      </c>
+      <c r="C214" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s">
+        <v>432</v>
+      </c>
+      <c r="B215" t="s">
+        <v>433</v>
+      </c>
+      <c r="C215" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s">
+        <v>434</v>
+      </c>
+      <c r="B216" t="s">
+        <v>435</v>
+      </c>
+      <c r="C216" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s">
+        <v>436</v>
+      </c>
+      <c r="B217" t="s">
+        <v>437</v>
+      </c>
+      <c r="C217" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s">
+        <v>438</v>
+      </c>
+      <c r="B218" t="s">
+        <v>439</v>
+      </c>
+      <c r="C218" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s">
+        <v>440</v>
+      </c>
+      <c r="B219" t="s">
+        <v>441</v>
+      </c>
+      <c r="C219" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s">
+        <v>442</v>
+      </c>
+      <c r="B220" t="s">
+        <v>443</v>
+      </c>
+      <c r="C220" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s">
+        <v>444</v>
+      </c>
+      <c r="B221" t="s">
+        <v>445</v>
+      </c>
+      <c r="C221" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s">
+        <v>446</v>
+      </c>
+      <c r="B222" t="s">
+        <v>447</v>
+      </c>
+      <c r="C222" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s">
+        <v>448</v>
+      </c>
+      <c r="B223" t="s">
+        <v>449</v>
+      </c>
+      <c r="C223" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s">
+        <v>450</v>
+      </c>
+      <c r="B224" t="s">
+        <v>451</v>
+      </c>
+      <c r="C224" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s">
+        <v>452</v>
+      </c>
+      <c r="B225" t="s">
+        <v>453</v>
+      </c>
+      <c r="C225" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s">
+        <v>454</v>
+      </c>
+      <c r="B226" t="s">
+        <v>455</v>
+      </c>
+      <c r="C226" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s">
+        <v>456</v>
+      </c>
+      <c r="B227" t="s">
+        <v>457</v>
+      </c>
+      <c r="C227" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s">
+        <v>458</v>
+      </c>
+      <c r="B228" t="s">
+        <v>459</v>
+      </c>
+      <c r="C228" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s">
+        <v>460</v>
+      </c>
+      <c r="B229" t="s">
+        <v>461</v>
+      </c>
+      <c r="C229" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s">
+        <v>462</v>
+      </c>
+      <c r="B230" t="s">
+        <v>463</v>
+      </c>
+      <c r="C230" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s">
+        <v>464</v>
+      </c>
+      <c r="B231" t="s">
+        <v>465</v>
+      </c>
+      <c r="C231" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s">
+        <v>466</v>
+      </c>
+      <c r="B232" t="s">
+        <v>467</v>
+      </c>
+      <c r="C232" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s">
+        <v>468</v>
+      </c>
+      <c r="B233" t="s">
+        <v>469</v>
+      </c>
+      <c r="C233" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s">
+        <v>470</v>
+      </c>
+      <c r="B234" t="s">
+        <v>471</v>
+      </c>
+      <c r="C234" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s">
+        <v>472</v>
+      </c>
+      <c r="B235" t="s">
+        <v>473</v>
+      </c>
+      <c r="C235" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s">
+        <v>474</v>
+      </c>
+      <c r="B236" t="s">
+        <v>475</v>
+      </c>
+      <c r="C236" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s">
+        <v>476</v>
+      </c>
+      <c r="B237" t="s">
+        <v>477</v>
+      </c>
+      <c r="C237" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s">
+        <v>478</v>
+      </c>
+      <c r="B238" t="s">
+        <v>479</v>
+      </c>
+      <c r="C238" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="s">
+        <v>480</v>
+      </c>
+      <c r="B239" t="s">
+        <v>481</v>
+      </c>
+      <c r="C239" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s">
+        <v>482</v>
+      </c>
+      <c r="B240" t="s">
+        <v>483</v>
+      </c>
+      <c r="C240" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s">
+        <v>484</v>
+      </c>
+      <c r="B241" t="s">
+        <v>485</v>
+      </c>
+      <c r="C241" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s">
+        <v>486</v>
+      </c>
+      <c r="B242" t="s">
+        <v>487</v>
+      </c>
+      <c r="C242" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s">
+        <v>488</v>
+      </c>
+      <c r="B243" t="s">
+        <v>489</v>
+      </c>
+      <c r="C243" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s">
+        <v>490</v>
+      </c>
+      <c r="B244" t="s">
+        <v>491</v>
+      </c>
+      <c r="C244" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s">
+        <v>492</v>
+      </c>
+      <c r="B245" t="s">
+        <v>493</v>
+      </c>
+      <c r="C245" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s">
+        <v>494</v>
+      </c>
+      <c r="B246" t="s">
+        <v>495</v>
+      </c>
+      <c r="C246" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s">
+        <v>496</v>
+      </c>
+      <c r="B247" t="s">
+        <v>497</v>
+      </c>
+      <c r="C247" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s">
+        <v>498</v>
+      </c>
+      <c r="B248" t="s">
+        <v>499</v>
+      </c>
+      <c r="C248" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s">
+        <v>500</v>
+      </c>
+      <c r="B249" t="s">
+        <v>501</v>
+      </c>
+      <c r="C249" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s">
+        <v>502</v>
+      </c>
+      <c r="B250" t="s">
+        <v>503</v>
+      </c>
+      <c r="C250" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s">
+        <v>504</v>
+      </c>
+      <c r="B251" t="s">
+        <v>505</v>
+      </c>
+      <c r="C251" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s">
+        <v>506</v>
+      </c>
+      <c r="B252" t="s">
+        <v>507</v>
+      </c>
+      <c r="C252" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s">
+        <v>508</v>
+      </c>
+      <c r="B253" t="s">
+        <v>509</v>
+      </c>
+      <c r="C253" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s">
+        <v>510</v>
+      </c>
+      <c r="B254" t="s">
+        <v>511</v>
+      </c>
+      <c r="C254" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s">
+        <v>512</v>
+      </c>
+      <c r="B255" t="s">
+        <v>513</v>
+      </c>
+      <c r="C255" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s">
+        <v>514</v>
+      </c>
+      <c r="B256" t="s">
+        <v>515</v>
+      </c>
+      <c r="C256" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s">
+        <v>517</v>
+      </c>
+      <c r="B257" t="s">
+        <v>518</v>
+      </c>
+      <c r="C257" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s">
+        <v>520</v>
+      </c>
+      <c r="B258" t="s">
+        <v>521</v>
+      </c>
+      <c r="C258" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s">
+        <v>523</v>
+      </c>
+      <c r="B259" t="s">
+        <v>524</v>
+      </c>
+      <c r="C259" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s">
+        <v>525</v>
+      </c>
+      <c r="B260" t="s">
+        <v>526</v>
+      </c>
+      <c r="C260" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s">
+        <v>527</v>
+      </c>
+      <c r="B261" t="s">
+        <v>528</v>
+      </c>
+      <c r="C261" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s">
+        <v>529</v>
+      </c>
+      <c r="B262" t="s">
+        <v>530</v>
+      </c>
+      <c r="C262" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s">
+        <v>531</v>
+      </c>
+      <c r="B263" t="s">
+        <v>532</v>
+      </c>
+      <c r="C263" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s">
+        <v>533</v>
+      </c>
+      <c r="B264" t="s">
+        <v>534</v>
+      </c>
+      <c r="C264" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s">
+        <v>535</v>
+      </c>
+      <c r="B265" t="s">
+        <v>536</v>
+      </c>
+      <c r="C265" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s">
+        <v>537</v>
+      </c>
+      <c r="B266" t="s">
+        <v>538</v>
+      </c>
+      <c r="C266" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s">
+        <v>539</v>
+      </c>
+      <c r="B267" t="s">
+        <v>540</v>
+      </c>
+      <c r="C267" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s">
+        <v>541</v>
+      </c>
+      <c r="B268" t="s">
+        <v>542</v>
+      </c>
+      <c r="C268" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s">
+        <v>543</v>
+      </c>
+      <c r="B269" t="s">
+        <v>544</v>
+      </c>
+      <c r="C269" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s">
+        <v>545</v>
+      </c>
+      <c r="B270" t="s">
+        <v>546</v>
+      </c>
+      <c r="C270" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s">
+        <v>547</v>
+      </c>
+      <c r="B271" t="s">
+        <v>548</v>
+      </c>
+      <c r="C271" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="s">
+        <v>550</v>
+      </c>
+      <c r="B272" t="s">
+        <v>551</v>
+      </c>
+      <c r="C272" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="s">
+        <v>552</v>
+      </c>
+      <c r="B273" t="s">
+        <v>553</v>
+      </c>
+      <c r="C273" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="s">
+        <v>554</v>
+      </c>
+      <c r="B274" t="s">
+        <v>555</v>
+      </c>
+      <c r="C274" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s">
+        <v>556</v>
+      </c>
+      <c r="B275" t="s">
+        <v>557</v>
+      </c>
+      <c r="C275" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s">
+        <v>558</v>
+      </c>
+      <c r="B276" t="s">
+        <v>559</v>
+      </c>
+      <c r="C276" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s">
+        <v>560</v>
+      </c>
+      <c r="B277" t="s">
+        <v>561</v>
+      </c>
+      <c r="C277" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s">
+        <v>562</v>
+      </c>
+      <c r="B278" t="s">
+        <v>563</v>
+      </c>
+      <c r="C278" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="s">
+        <v>564</v>
+      </c>
+      <c r="B279" t="s">
+        <v>565</v>
+      </c>
+      <c r="C279" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s">
+        <v>566</v>
+      </c>
+      <c r="B280" t="s">
+        <v>567</v>
+      </c>
+      <c r="C280" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s">
+        <v>568</v>
+      </c>
+      <c r="B281" t="s">
+        <v>569</v>
+      </c>
+      <c r="C281" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s">
+        <v>571</v>
+      </c>
+      <c r="B282" t="s">
+        <v>572</v>
+      </c>
+      <c r="C282" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s">
+        <v>573</v>
+      </c>
+      <c r="B283" t="s">
+        <v>574</v>
+      </c>
+      <c r="C283" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s">
+        <v>576</v>
+      </c>
+      <c r="B284" t="s">
+        <v>577</v>
+      </c>
+      <c r="C284" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="s">
+        <v>578</v>
+      </c>
+      <c r="B285" t="s">
+        <v>579</v>
+      </c>
+      <c r="C285" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s">
+        <v>580</v>
+      </c>
+      <c r="B286" t="s">
+        <v>581</v>
+      </c>
+      <c r="C286" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="s">
+        <v>582</v>
+      </c>
+      <c r="B287" t="s">
+        <v>583</v>
+      </c>
+      <c r="C287" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="s">
+        <v>584</v>
+      </c>
+      <c r="B288" t="s">
+        <v>585</v>
+      </c>
+      <c r="C288" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="s">
+        <v>586</v>
+      </c>
+      <c r="B289" t="s">
+        <v>587</v>
+      </c>
+      <c r="C289" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="s">
+        <v>589</v>
+      </c>
+      <c r="B290" t="s">
+        <v>590</v>
+      </c>
+      <c r="C290" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="s">
+        <v>591</v>
+      </c>
+      <c r="B291" t="s">
+        <v>592</v>
+      </c>
+      <c r="C291" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="s">
+        <v>593</v>
+      </c>
+      <c r="B292" t="s">
+        <v>594</v>
+      </c>
+      <c r="C292" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="s">
+        <v>595</v>
+      </c>
+      <c r="B293" t="s">
+        <v>596</v>
+      </c>
+      <c r="C293" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="s">
+        <v>597</v>
+      </c>
+      <c r="B294" t="s">
+        <v>598</v>
+      </c>
+      <c r="C294" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="s">
+        <v>599</v>
+      </c>
+      <c r="B295" t="s">
+        <v>600</v>
+      </c>
+      <c r="C295" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="s">
+        <v>601</v>
+      </c>
+      <c r="B296" t="s">
+        <v>602</v>
+      </c>
+      <c r="C296" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="s">
+        <v>603</v>
+      </c>
+      <c r="B297" t="s">
+        <v>604</v>
+      </c>
+      <c r="C297" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="s">
+        <v>605</v>
+      </c>
+      <c r="B298" t="s">
+        <v>606</v>
+      </c>
+      <c r="C298" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="s">
+        <v>607</v>
+      </c>
+      <c r="B299" t="s">
+        <v>608</v>
+      </c>
+      <c r="C299" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="s">
+        <v>609</v>
+      </c>
+      <c r="B300" t="s">
+        <v>610</v>
+      </c>
+      <c r="C300" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="s">
+        <v>611</v>
+      </c>
+      <c r="B301" t="s">
+        <v>612</v>
+      </c>
+      <c r="C301" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="s">
+        <v>613</v>
+      </c>
+      <c r="B302" t="s">
+        <v>614</v>
+      </c>
+      <c r="C302" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="s">
+        <v>615</v>
+      </c>
+      <c r="B303" t="s">
+        <v>616</v>
+      </c>
+      <c r="C303" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="s">
+        <v>617</v>
+      </c>
+      <c r="B304" t="s">
+        <v>618</v>
+      </c>
+      <c r="C304" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="s">
+        <v>619</v>
+      </c>
+      <c r="B305" t="s">
+        <v>620</v>
+      </c>
+      <c r="C305" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="s">
+        <v>622</v>
+      </c>
+      <c r="B306" t="s">
+        <v>623</v>
+      </c>
+      <c r="C306" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="s">
+        <v>624</v>
+      </c>
+      <c r="B307" t="s">
+        <v>625</v>
+      </c>
+      <c r="C307" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="s">
+        <v>626</v>
+      </c>
+      <c r="B308" t="s">
+        <v>627</v>
+      </c>
+      <c r="C308" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="s">
+        <v>628</v>
+      </c>
+      <c r="B309" t="s">
+        <v>629</v>
+      </c>
+      <c r="C309" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="s">
+        <v>630</v>
+      </c>
+      <c r="B310" t="s">
+        <v>631</v>
+      </c>
+      <c r="C310" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="s">
+        <v>632</v>
+      </c>
+      <c r="B311" t="s">
+        <v>633</v>
+      </c>
+      <c r="C311" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="s">
+        <v>634</v>
+      </c>
+      <c r="B312" t="s">
+        <v>635</v>
+      </c>
+      <c r="C312" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="s">
+        <v>636</v>
+      </c>
+      <c r="B313" t="s">
+        <v>637</v>
+      </c>
+      <c r="C313" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="s">
+        <v>638</v>
+      </c>
+      <c r="B314" t="s">
+        <v>639</v>
+      </c>
+      <c r="C314" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="s">
+        <v>640</v>
+      </c>
+      <c r="B315" t="s">
+        <v>641</v>
+      </c>
+      <c r="C315" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="s">
+        <v>642</v>
+      </c>
+      <c r="B316" t="s">
+        <v>643</v>
+      </c>
+      <c r="C316" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="s">
+        <v>644</v>
+      </c>
+      <c r="B317" t="s">
+        <v>645</v>
+      </c>
+      <c r="C317" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="s">
+        <v>646</v>
+      </c>
+      <c r="B318" t="s">
+        <v>647</v>
+      </c>
+      <c r="C318" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="s">
+        <v>648</v>
+      </c>
+      <c r="B319" t="s">
+        <v>649</v>
+      </c>
+      <c r="C319" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="s">
+        <v>650</v>
+      </c>
+      <c r="B320" t="s">
+        <v>651</v>
+      </c>
+      <c r="C320" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="s">
+        <v>652</v>
+      </c>
+      <c r="B321" t="s">
+        <v>653</v>
+      </c>
+      <c r="C321" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="s">
+        <v>654</v>
+      </c>
+      <c r="B322" t="s">
+        <v>655</v>
+      </c>
+      <c r="C322" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="s">
+        <v>657</v>
+      </c>
+      <c r="B323" t="s">
+        <v>658</v>
+      </c>
+      <c r="C323" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="s">
+        <v>659</v>
+      </c>
+      <c r="B324" t="s">
+        <v>660</v>
+      </c>
+      <c r="C324" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="s">
+        <v>661</v>
+      </c>
+      <c r="B325" t="s">
+        <v>662</v>
+      </c>
+      <c r="C325" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="s">
+        <v>663</v>
+      </c>
+      <c r="B326" t="s">
+        <v>664</v>
+      </c>
+      <c r="C326" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="s">
+        <v>665</v>
+      </c>
+      <c r="B327" t="s">
+        <v>666</v>
+      </c>
+      <c r="C327" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="s">
+        <v>668</v>
+      </c>
+      <c r="B328" t="s">
+        <v>669</v>
+      </c>
+      <c r="C328" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="s">
+        <v>670</v>
+      </c>
+      <c r="B329" t="s">
+        <v>671</v>
+      </c>
+      <c r="C329" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="s">
+        <v>672</v>
+      </c>
+      <c r="B330" t="s">
+        <v>673</v>
+      </c>
+      <c r="C330" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="s">
+        <v>674</v>
+      </c>
+      <c r="B331" t="s">
+        <v>675</v>
+      </c>
+      <c r="C331" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="s">
+        <v>676</v>
+      </c>
+      <c r="B332" t="s">
+        <v>677</v>
+      </c>
+      <c r="C332" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="s">
+        <v>678</v>
+      </c>
+      <c r="B333" t="s">
+        <v>679</v>
+      </c>
+      <c r="C333" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="s">
+        <v>681</v>
+      </c>
+      <c r="B334" t="s">
+        <v>682</v>
+      </c>
+      <c r="C334" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="s">
+        <v>684</v>
+      </c>
+      <c r="B335" t="s">
+        <v>685</v>
+      </c>
+      <c r="C335" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="s">
+        <v>686</v>
+      </c>
+      <c r="B336" t="s">
+        <v>687</v>
+      </c>
+      <c r="C336" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="s">
+        <v>688</v>
+      </c>
+      <c r="B337" t="s">
+        <v>689</v>
+      </c>
+      <c r="C337" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="s">
+        <v>690</v>
+      </c>
+      <c r="B338" t="s">
+        <v>691</v>
+      </c>
+      <c r="C338" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="s">
+        <v>693</v>
+      </c>
+      <c r="B339" t="s">
+        <v>694</v>
+      </c>
+      <c r="C339" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="s">
+        <v>695</v>
+      </c>
+      <c r="B340" t="s">
+        <v>696</v>
+      </c>
+      <c r="C340" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="s">
+        <v>697</v>
+      </c>
+      <c r="B341" t="s">
+        <v>698</v>
+      </c>
+      <c r="C341" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="s">
+        <v>699</v>
+      </c>
+      <c r="B342" t="s">
+        <v>700</v>
+      </c>
+      <c r="C342" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="s">
+        <v>701</v>
+      </c>
+      <c r="B343" t="s">
+        <v>702</v>
+      </c>
+      <c r="C343" t="s">
+        <v>692</v>
       </c>
     </row>
   </sheetData>

--- a/modules/vas/vas_report_labels.xlsx
+++ b/modules/vas/vas_report_labels.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="731">
   <si>
     <t xml:space="preserve">question_code</t>
   </si>
@@ -80,192 +80,195 @@
     <t xml:space="preserve">PrepaidElectricity_Purchased</t>
   </si>
   <si>
-    <t xml:space="preserve">Did you purchase prepaid electricity in the past 12 months?</t>
+    <t xml:space="preserve">Have you purchased prepaid electricity in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">from the kept structure, 18 Aug 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrepaidElectricity_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepaid electricity purchase frequency per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrepaidElectricity_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly prepaid electricity spend (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrepaidElectricity_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average prepaid electricity transaction value (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrepaidElectricity_Own_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepaid electricity purchase frequency per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrepaidElectricity_Own_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly prepaid electricity spend (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrepaidElectricity_Own_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average prepaid electricity transaction value (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrepaidElectricity_Oth_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepaid electricity purchase frequency per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrepaidElectricity_Oth_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly prepaid electricity spend (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrepaidElectricity_Oth_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average prepaid electricity transaction value (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airtime_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Have you purchased prepaid airtime in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airtime_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepaid airtime purchase frequency per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airtime_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly prepaid airtime spend (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airtime_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average prepaid airtime transaction value (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airtime_Own_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepaid airtime purchase frequency per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airtime_Own_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly prepaid airtime spend (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airtime_Own_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average prepaid airtime transaction value (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airtime_Oth_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepaid airtime purchase frequency per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airtime_Oth_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly prepaid airtime spend (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airtime_Oth_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average prepaid airtime transaction value (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Have you purchased prepaid data in the past 12 months?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data_Total_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepaid data purchase frequency per month (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data_Total_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly prepaid data spend (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data_Total_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average prepaid data transaction value (all purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data_Own_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepaid data purchase frequency per month (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data_Own_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly prepaid data spend (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data_Own_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average prepaid data transaction value (for self)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data_Oth_TxnPerMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepaid data purchase frequency per month (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data_Oth_MonthlySpend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly prepaid data spend (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data_Oth_SpendPerTxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average prepaid data transaction value (for others)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DigitalVouchers_Purchased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you buy digital vouchers in the past 12 months?</t>
   </si>
   <si>
     <t xml:space="preserve">Crosstab planning, 14 Aug 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">PrepaidElectricity_Total_TxnPerMonth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of Prepaid electricity transactions per month (all purchases)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PrepaidElectricity_Total_MonthlySpend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prepaid electricity spend per month (all purchases)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PrepaidElectricity_Total_SpendPerTxn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average Prepaid electricity value per transaction (all purchases)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PrepaidElectricity_Own_TxnPerMonth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of Prepaid electricity transactions per month (for self)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PrepaidElectricity_Own_MonthlySpend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prepaid electricity spend per month (for self)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PrepaidElectricity_Own_SpendPerTxn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average Prepaid electricity value per transaction (for self)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PrepaidElectricity_Oth_TxnPerMonth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of Prepaid electricity transactions per month (for others)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PrepaidElectricity_Oth_MonthlySpend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prepaid electricity spend per month (for others)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PrepaidElectricity_Oth_SpendPerTxn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average Prepaid electricity value per transaction (for others)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airtime_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Did you buy airtime in the past 12 months?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airtime_Total_TxnPerMonth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of Prepaid airtime transactions per month (all purchases)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airtime_Total_MonthlySpend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prepaid airtime spend per month (all purchases)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airtime_Total_SpendPerTxn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average Prepaid airtime value per transaction (all purchases)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airtime_Own_TxnPerMonth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of Prepaid airtime transactions per month (for self)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airtime_Own_MonthlySpend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prepaid airtime spend per month (for self)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airtime_Own_SpendPerTxn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average Prepaid airtime value per transaction (for self)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airtime_Oth_TxnPerMonth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of Prepaid airtime transactions per month (for others)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airtime_Oth_MonthlySpend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prepaid airtime spend per month (for others)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airtime_Oth_SpendPerTxn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average Prepaid airtime value per transaction (for others)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Did you buy data in the past 12 months?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data_Total_TxnPerMonth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of Prepaid data transactions per month (all purchases)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data_Total_MonthlySpend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prepaid data spend per month (all purchases)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data_Total_SpendPerTxn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average Prepaid data value per transaction (all purchases)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data_Own_TxnPerMonth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of Prepaid data transactions per month (for self)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data_Own_MonthlySpend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prepaid data spend per month (for self)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data_Own_SpendPerTxn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average Prepaid data value per transaction (for self)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data_Oth_TxnPerMonth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of Prepaid data transactions per month (for others)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data_Oth_MonthlySpend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prepaid data spend per month (for others)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data_Oth_SpendPerTxn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average Prepaid data value per transaction (for others)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DigitalVouchers_Purchased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Did you buy digital vouchers in the past 12 months?</t>
-  </si>
-  <si>
     <t xml:space="preserve">DigitalVouchers_Total_TxnPerMonth</t>
   </si>
   <si>
@@ -383,127 +386,127 @@
     <t xml:space="preserve">BillTraffic_Purchased</t>
   </si>
   <si>
-    <t xml:space="preserve">Did you pay traffic fines in the past 12 months?</t>
+    <t xml:space="preserve">Have you paid traffic fines in the past 12 months?</t>
   </si>
   <si>
     <t xml:space="preserve">BillTraffic_Total_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Traffic fines transactions per month (all spend)</t>
+    <t xml:space="preserve">Traffic fines payment frequency per month (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillTraffic_Total_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Traffic fines spend per month (all spend)</t>
+    <t xml:space="preserve">Monthly traffic fines spend (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillTraffic_Total_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Traffic fines value per transaction (all spend)</t>
+    <t xml:space="preserve">Average traffic fines transaction value (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillTraffic_Own_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Traffic fines transactions per month (for self)</t>
+    <t xml:space="preserve">Traffic fines payment frequency per month (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillTraffic_Own_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Traffic fines spend per month (for self)</t>
+    <t xml:space="preserve">Monthly traffic fines spend (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillTraffic_Own_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Traffic fines value per transaction (for self)</t>
+    <t xml:space="preserve">Average traffic fines transaction value (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillTraffic_Oth_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Traffic fines transactions per month (for others)</t>
+    <t xml:space="preserve">Traffic fines payment frequency per month (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillTraffic_Oth_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Traffic fines spend per month (for others)</t>
+    <t xml:space="preserve">Monthly traffic fines spend (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillTraffic_Oth_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Traffic fines value per transaction (for others)</t>
+    <t xml:space="preserve">Average traffic fines transaction value (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillClothing_Purchased</t>
   </si>
   <si>
-    <t xml:space="preserve">Did you pay a clothing/fashion account in the past 12 months?</t>
+    <t xml:space="preserve">Have you paid a clothing or fashion account in the past 12 months using a VAS method?</t>
   </si>
   <si>
     <t xml:space="preserve">BillClothing_Total_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Clothing/fashion transactions per month (all spend)</t>
+    <t xml:space="preserve">Clothing/fashion payment account frequency per month (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillClothing_Total_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Clothing/fashion spend per month (all spend)</t>
+    <t xml:space="preserve">Monthly clothing/fashion account payment (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillClothing_Total_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Clothing/fashion value per transaction (all spend)</t>
+    <t xml:space="preserve">Average clothing/fashion account transaction value (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillClothing_Own_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Clothing/fashion transactions per month (for self)</t>
+    <t xml:space="preserve">Clothing/fashion payment account frequency per month (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillClothing_Own_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Clothing/fashion spend per month (for self)</t>
+    <t xml:space="preserve">Monthly clothing/fashion account payment (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillClothing_Own_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Clothing/fashion value per transaction (for self)</t>
+    <t xml:space="preserve">Average clothing/fashion account transaction value (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillClothing_Oth_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Clothing/fashion transactions per month (for others)</t>
+    <t xml:space="preserve">Clothing/fashion payment account frequency per month (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillClothing_Oth_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Clothing/fashion spend per month (for others)</t>
+    <t xml:space="preserve">Monthly clothing/fashion account spend (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillClothing_Oth_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Clothing/fashion value per transaction (for others)</t>
+    <t xml:space="preserve">Average clothing/fashion account transaction value (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillFurniture_Purchased</t>
   </si>
   <si>
-    <t xml:space="preserve">Did you pay a furniture account in the past 12 months?</t>
+    <t xml:space="preserve">Have you paid a furniture account in the past 12 months using a VAS method?</t>
   </si>
   <si>
     <t xml:space="preserve">BillFurniture_Total_TxnPerMonth</t>
@@ -515,709 +518,709 @@
     <t xml:space="preserve">BillFurniture_Total_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Furniture spend per month (all spend)</t>
+    <t xml:space="preserve">Monthly furniture account payment (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillFurniture_Total_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Furniture value per transaction (all spend)</t>
+    <t xml:space="preserve">Average furniture account transaction value (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillFurniture_Own_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Furniture transactions per month (for self)</t>
+    <t xml:space="preserve">Furniture payment account frequency per month (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillFurniture_Own_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Furniture spend per month (for self)</t>
+    <t xml:space="preserve">Monthly furniture account payment (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillFurniture_Own_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Furniture value per transaction (for self)</t>
+    <t xml:space="preserve">Average furniture account transaction value (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillFurniture_Oth_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Furniture transactions per month (for others)</t>
+    <t xml:space="preserve">Furniture account payment frequency per month (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillFurniture_Oth_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Furniture spend per month (for others)</t>
+    <t xml:space="preserve">Monthly furniture account payment(for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillFurniture_Oth_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Furniture value per transaction (for others)</t>
+    <t xml:space="preserve">Average furniture account transaction value (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillEducation_Purchased</t>
   </si>
   <si>
-    <t xml:space="preserve">Did you pay education fees in the past 12 months?</t>
+    <t xml:space="preserve">Have you paid education fees in the past 12 months using a VAS method?</t>
   </si>
   <si>
     <t xml:space="preserve">BillEducation_Total_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Education transactions per month (all spend)</t>
+    <t xml:space="preserve">Education payment frequency per month (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillEducation_Total_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Education spend per month (all spend)</t>
+    <t xml:space="preserve">Monthly education payment (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillEducation_Total_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Education value per transaction (all spend)</t>
+    <t xml:space="preserve">Average education transaction value (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillEducation_Own_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Education transactions per month (for self)</t>
+    <t xml:space="preserve">Education payment frequency per month (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillEducation_Own_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Education spend per month (for self)</t>
+    <t xml:space="preserve">Monthly education payment (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillEducation_Own_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Education value per transaction (for self)</t>
+    <t xml:space="preserve">Average education transaction value (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillEducation_Oth_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Education transactions per month (for others)</t>
+    <t xml:space="preserve">Education payment frequency per month (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillEducation_Oth_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Education spend per month (for others)</t>
+    <t xml:space="preserve">Monthly education payment (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillEducation_Oth_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Education value per transaction (for others)</t>
+    <t xml:space="preserve">Average education transaction value (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillHealth_Purchased</t>
   </si>
   <si>
-    <t xml:space="preserve">Did you pay health bills in the past 12 months?</t>
+    <t xml:space="preserve">Have you paid health bills in the past 12 months using a VAS method?</t>
   </si>
   <si>
     <t xml:space="preserve">BillHealth_Total_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Health transactions per month (all spend)</t>
+    <t xml:space="preserve">Health payment frequency per month (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillHealth_Total_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Health spend per month (all spend)</t>
+    <t xml:space="preserve">Monthly health spend (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillHealth_Total_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Health value per transaction (all spend)</t>
+    <t xml:space="preserve">Average health transaction value (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillHealth_Own_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Health transactions per month (for self)</t>
+    <t xml:space="preserve">Health payment frequency per month (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillHealth_Own_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Health spend per month (for self)</t>
+    <t xml:space="preserve">Monthly health spend (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillHealth_Own_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Health value per transaction (for self)</t>
+    <t xml:space="preserve">Average health transaction value (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillHealth_Oth_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Health transactions per month (for others)</t>
+    <t xml:space="preserve">Health payment frequency per month (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillHealth_Oth_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Health spend per month (for others)</t>
+    <t xml:space="preserve">Monthly health spend (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillHealth_Oth_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Health value per transaction (for others)</t>
+    <t xml:space="preserve">Average health transaction value (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillRetail_Purchased</t>
   </si>
   <si>
-    <t xml:space="preserve">Did you pay a retail credit account in the past 12 months?</t>
+    <t xml:space="preserve">Have you paid a retail credit account in the past 12 months using a VAS method?</t>
   </si>
   <si>
     <t xml:space="preserve">BillRetail_Total_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Retail credit transactions per month (all spend)</t>
+    <t xml:space="preserve">Retail credit account payment frequency per month (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillRetail_Total_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Retail credit spend per month (all spend)</t>
+    <t xml:space="preserve">Monthly retail credit account payment (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillRetail_Total_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Retail credit value per transaction (all spend)</t>
+    <t xml:space="preserve">Average retail credit account transaction value (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillRetail_Own_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Retail credit transactions per month (for self)</t>
+    <t xml:space="preserve">Retail credit account payment frequency per month (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillRetail_Own_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Retail credit spend per month (for self)</t>
+    <t xml:space="preserve">Monthly retail credit account payment (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillRetail_Own_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Retail credit value per transaction (for self)</t>
+    <t xml:space="preserve">Average retail credit account transaction value (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillRetail_Oth_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Retail credit transactions per month (for others)</t>
+    <t xml:space="preserve">Retail credit payment account frequency per month (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillRetail_Oth_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Retail credit spend per month (for others)</t>
+    <t xml:space="preserve">Monthly retail credit account payment (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillRetail_Oth_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Retail credit value per transaction (for others)</t>
+    <t xml:space="preserve">Average retail account credit transaction value (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillOther_Purchased</t>
   </si>
   <si>
-    <t xml:space="preserve">Did you pay other bills in the past 12 months?</t>
+    <t xml:space="preserve">Have you paid other bills in the past 12 months?</t>
   </si>
   <si>
     <t xml:space="preserve">BillOther_Total_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Other bills transactions per month (all spend)</t>
+    <t xml:space="preserve">Other bills payment frequency per month (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillOther_Total_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Other bills spend per month (all spend)</t>
+    <t xml:space="preserve">Monthly other bills spend (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillOther_Total_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Other bills value per transaction (all spend)</t>
+    <t xml:space="preserve">Average other bills transaction value (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillOther_Own_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Other bills transactions per month (for self)</t>
+    <t xml:space="preserve">Other bills payment frequency per month (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillOther_Own_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Other bills spend per month (for self)</t>
+    <t xml:space="preserve">Monthly other bills spend (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillOther_Own_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Other bills value per transaction (for self)</t>
+    <t xml:space="preserve">Average other bills transaction value (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillOther_Oth_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Other bills transactions per month (for others)</t>
+    <t xml:space="preserve">Other bills payment frequency per month (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillOther_Oth_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Other bills spend per month (for others)</t>
+    <t xml:space="preserve">Monthly other bills spend (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillOther_Oth_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Other bills value per transaction (for others)</t>
+    <t xml:space="preserve">Average other bills transaction value (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillDSTV_Purchased</t>
   </si>
   <si>
-    <t xml:space="preserve">Did you pay DSTV / Multichoice in the past 12 months?</t>
+    <t xml:space="preserve">Have you paid a DSTV / Multichoice account in the past 12 months using a VAS method?</t>
   </si>
   <si>
     <t xml:space="preserve">BillDSTV_Total_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of DSTV / Multichoice transactions per month (all spend)</t>
+    <t xml:space="preserve">DSTV / Multichoice payment frequency per month (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillDSTV_Total_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">DSTV / Multichoice spend per month (all spend)</t>
+    <t xml:space="preserve">Monthly DSTV / Multichoice payment (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillDSTV_Total_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average DSTV / Multichoice value per transaction (all spend)</t>
+    <t xml:space="preserve">Average DSTV / Multichoice transaction value (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillDSTV_Own_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of DSTV / Multichoice transactions per month (for self)</t>
+    <t xml:space="preserve">DSTV / Multichoice payment frequency per month (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillDSTV_Own_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">DSTV / Multichoice spend per month (for self)</t>
+    <t xml:space="preserve">Monthly DSTV / Multichoice payment (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillDSTV_Own_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average DSTV / Multichoice value per transaction (for self)</t>
+    <t xml:space="preserve">Average DSTV / Multichoice transaction value (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillDSTV_Oth_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of DSTV / Multichoice transactions per month (for others)</t>
+    <t xml:space="preserve">DSTV / Multichoice payment frequency per month (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillDSTV_Oth_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">DSTV / Multichoice spend per month (for others)</t>
+    <t xml:space="preserve">Monthly DSTV / Multichoice payment (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillDSTV_Oth_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average DSTV / Multichoice value per transaction (for others)</t>
+    <t xml:space="preserve">Average DSTV / Multichoice transaction value (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillMunicipal_Purchased</t>
   </si>
   <si>
-    <t xml:space="preserve">Did you pay a municipal account in the past 12 months?</t>
+    <t xml:space="preserve">Have you paid a municipal account in the past 12 months using a VAS method?</t>
   </si>
   <si>
     <t xml:space="preserve">BillMunicipal_Total_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Municipal account transactions per month (all spend)</t>
+    <t xml:space="preserve">Municipal account payment frequency per month (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillMunicipal_Total_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Municipal account spend per month (all spend)</t>
+    <t xml:space="preserve">Monthly municipal account payment (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillMunicipal_Total_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Municipal account value per transaction (all spend)</t>
+    <t xml:space="preserve">Average municipal account transaction value (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillMunicipal_Own_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Municipal account transactions per month (for self)</t>
+    <t xml:space="preserve">Municipal account payment frequency per month (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillMunicipal_Own_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Municipal account spend per month (for self)</t>
+    <t xml:space="preserve">Monthly municipal account spend (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillMunicipal_Own_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Municipal account value per transaction (for self)</t>
+    <t xml:space="preserve">Average municipal account transaction value (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillMunicipal_Oth_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Municipal account transactions per month (for others)</t>
+    <t xml:space="preserve">Municipal account payment frequency per month (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillMunicipal_Oth_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Municipal account spend per month (for others)</t>
+    <t xml:space="preserve">Monthly municipal account spend (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillMunicipal_Oth_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Municipal account value per transaction (for others)</t>
+    <t xml:space="preserve">Average municipal account transaction value (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillTelkom_Purchased</t>
   </si>
   <si>
-    <t xml:space="preserve">Did you pay Telkom / cellphone in the past 12 months?</t>
+    <t xml:space="preserve">Have you paid a Telkom or cellphone bill in the past 12 months using a VAS method?</t>
   </si>
   <si>
     <t xml:space="preserve">BillTelkom_Total_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Telkom / cellphone transactions per month (all spend)</t>
+    <t xml:space="preserve">Telkom / cellphone payment frequency per month (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillTelkom_Total_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Telkom / cellphone spend per month (all spend)</t>
+    <t xml:space="preserve">Monthly Telkom / cellphone spend (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillTelkom_Total_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Telkom / cellphone value per transaction (all spend)</t>
+    <t xml:space="preserve">Average Telkom / cellphone transaction value (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillTelkom_Own_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Telkom / cellphone transactions per month (for self)</t>
+    <t xml:space="preserve">Telkom / cellphone payment frequency per month (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillTelkom_Own_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Telkom / cellphone spend per month (for self)</t>
+    <t xml:space="preserve">Monthly Telkom / cellphone payment (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillTelkom_Own_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Telkom / cellphone value per transaction (for self)</t>
+    <t xml:space="preserve">Average Telkom / cellphone transaction value (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillTelkom_Oth_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Telkom / cellphone transactions per month (for others)</t>
+    <t xml:space="preserve">Telkom / cellphone payment frequency per month (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillTelkom_Oth_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Telkom / cellphone spend per month (for others)</t>
+    <t xml:space="preserve">Monthly Telkom / cellphone spend (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillTelkom_Oth_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Telkom / cellphone value per transaction (for others)</t>
+    <t xml:space="preserve">Average Telkom / cellphone transaction value (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillInsurance_Purchased</t>
   </si>
   <si>
-    <t xml:space="preserve">Did you pay insurance / funeral in the past 12 months?</t>
+    <t xml:space="preserve">Have you paid an insurance or funeral policy in the past 12 months using a VAS method?</t>
   </si>
   <si>
     <t xml:space="preserve">BillInsurance_Total_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Insurance / funeral transactions per month (all spend)</t>
+    <t xml:space="preserve">Insurance / funeral payment frequency per month (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillInsurance_Total_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Insurance / funeral spend per month (all spend)</t>
+    <t xml:space="preserve">Monthly insurance / funeral payment (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillInsurance_Total_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Insurance / funeral value per transaction (all spend)</t>
+    <t xml:space="preserve">Average insurance / funeral transaction value (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillInsurance_Own_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Insurance / funeral transactions per month (for self)</t>
+    <t xml:space="preserve">Insurance / funeral payment frequency per month (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillInsurance_Own_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Insurance / funeral spend per month (for self)</t>
+    <t xml:space="preserve">Monthly insurance / funeral payment (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillInsurance_Own_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Insurance / funeral value per transaction (for self)</t>
+    <t xml:space="preserve">Average insurance / funeral transaction value (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillInsurance_Oth_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Insurance / funeral transactions per month (for others)</t>
+    <t xml:space="preserve">Insurance / funeral payment frequency per month (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillInsurance_Oth_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Insurance / funeral spend per month (for others)</t>
+    <t xml:space="preserve">Monthly insurance / funeral payment (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillInsurance_Oth_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Insurance / funeral value per transaction (for others)</t>
+    <t xml:space="preserve">Average insurance / funeral transaction value (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillInternet_Purchased</t>
   </si>
   <si>
-    <t xml:space="preserve">Did you pay an internet subscription in the past 12 months?</t>
+    <t xml:space="preserve">Have you paid an internet subscription in the past 12 months using a VAS method?</t>
   </si>
   <si>
     <t xml:space="preserve">BillInternet_Total_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Internet subscription transactions per month (all spend)</t>
+    <t xml:space="preserve">Internet subscription payment frequency per month (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillInternet_Total_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Internet subscription spend per month (all spend)</t>
+    <t xml:space="preserve">Monthly internet subscription payment (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillInternet_Total_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Internet subscription value per transaction (all spend)</t>
+    <t xml:space="preserve">Average internet subscription transaction value (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillInternet_Own_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Internet subscription transactions per month (for self)</t>
+    <t xml:space="preserve">Internet subscription payment frequency per month (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillInternet_Own_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Internet subscription spend per month (for self)</t>
+    <t xml:space="preserve">Monthly internet subscription payment (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillInternet_Own_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Internet subscription value per transaction (for self)</t>
+    <t xml:space="preserve">Average internet subscription transaction value (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillInternet_Oth_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Internet subscription transactions per month (for others)</t>
+    <t xml:space="preserve">Internet subscription payment frequency per month (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillInternet_Oth_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Internet subscription spend per month (for others)</t>
+    <t xml:space="preserve">Monthly internet subscription payment (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillInternet_Oth_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Internet subscription value per transaction (for others)</t>
+    <t xml:space="preserve">Average internet subscription transaction value (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillVehicle_Purchased</t>
   </si>
   <si>
-    <t xml:space="preserve">Did you pay a vehicle licence in the past 12 months?</t>
+    <t xml:space="preserve">Have you paid for a vehicle licence in the past 12 months using a VAS method?</t>
   </si>
   <si>
     <t xml:space="preserve">BillVehicle_Total_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Vehicle licence transactions per month (all spend)</t>
+    <t xml:space="preserve">Vehicle licence payment frequency per month (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillVehicle_Total_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Vehicle licence spend per month (all spend)</t>
+    <t xml:space="preserve">Monthly vehicle licence payment (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillVehicle_Total_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Vehicle licence value per transaction (all spend)</t>
+    <t xml:space="preserve">Average vehicle licence transaction value (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillVehicle_Own_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Vehicle licence transactions per month (for self)</t>
+    <t xml:space="preserve">Vehicle licence payment frequency per month (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillVehicle_Own_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Vehicle licence spend per month (for self)</t>
+    <t xml:space="preserve">Monthly vehicle licence payment (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillVehicle_Own_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Vehicle licence value per transaction (for self)</t>
+    <t xml:space="preserve">Average vehicle licence transaction value (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillVehicle_Oth_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Vehicle licence transactions per month (for others)</t>
+    <t xml:space="preserve">Vehicle licence payment frequency per month (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillVehicle_Oth_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">Vehicle licence spend per month (for others)</t>
+    <t xml:space="preserve">Monthly vehicle licence payment (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillVehicle_Oth_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average Vehicle licence value per transaction (for others)</t>
+    <t xml:space="preserve">Average vehicle licence transaction value (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillTVLicence_Purchased</t>
   </si>
   <si>
-    <t xml:space="preserve">Did you pay a TV licence in the past 12 months?</t>
+    <t xml:space="preserve">Have you paid a TV licence in the past 12 months using a VAS method?</t>
   </si>
   <si>
     <t xml:space="preserve">BillTVLicence_Total_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of TV licence transactions per month (all spend)</t>
+    <t xml:space="preserve">TV licence payment frequency per month (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillTVLicence_Total_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">TV licence spend per month (all spend)</t>
+    <t xml:space="preserve">Monthly TV licence spend (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillTVLicence_Total_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average TV licence value per transaction (all spend)</t>
+    <t xml:space="preserve">Average TV licence transaction value (all payments)</t>
   </si>
   <si>
     <t xml:space="preserve">BillTVLicence_Own_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of TV licence transactions per month (for self)</t>
+    <t xml:space="preserve">TV licence payment frequency per month (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillTVLicence_Own_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">TV licence spend per month (for self)</t>
+    <t xml:space="preserve">Monthly TV licence spend (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillTVLicence_Own_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average TV licence value per transaction (for self)</t>
+    <t xml:space="preserve">Average TV licence transaction value (for self)</t>
   </si>
   <si>
     <t xml:space="preserve">BillTVLicence_Oth_TxnPerMonth</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of TV licence transactions per month (for others)</t>
+    <t xml:space="preserve">TV licence payment frequency per month (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillTVLicence_Oth_MonthlySpend</t>
   </si>
   <si>
-    <t xml:space="preserve">TV licence spend per month (for others)</t>
+    <t xml:space="preserve">Monthly TV licence spend (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">BillTVLicence_Oth_SpendPerTxn</t>
   </si>
   <si>
-    <t xml:space="preserve">Average TV licence value per transaction (for others)</t>
+    <t xml:space="preserve">Average TV licence transaction value (for others)</t>
   </si>
   <si>
     <t xml:space="preserve">Lotto_Purchased</t>
@@ -1598,13 +1601,13 @@
     <t xml:space="preserve">Airtime</t>
   </si>
   <si>
-    <t xml:space="preserve">Who have you bought airtime for? (multi-mentions possible)</t>
+    <t xml:space="preserve">Who prepaid airtime was purchased for?</t>
   </si>
   <si>
     <t xml:space="preserve">AirtimeChannelEver</t>
   </si>
   <si>
-    <t xml:space="preserve">Where do you buy prepaid airtime - all purchases</t>
+    <t xml:space="preserve">All prepaid airtime purchase channels used</t>
   </si>
   <si>
     <t xml:space="preserve">AirtimeChannelMain</t>
@@ -1616,25 +1619,25 @@
     <t xml:space="preserve">AirtimeChannelAlso</t>
   </si>
   <si>
-    <t xml:space="preserve">Where else do you buy prepaid airtime - apart from the channel used most often?</t>
+    <t xml:space="preserve">Where else do you buy prepaid airtime?</t>
   </si>
   <si>
     <t xml:space="preserve">AirtimeChannelOther</t>
   </si>
   <si>
-    <t xml:space="preserve">Where else have you bought prepaid airtime in the past 12 months?</t>
+    <t xml:space="preserve">Where else have you bought prepaid airtime in the past 12 months? (raw mentions)</t>
   </si>
   <si>
     <t xml:space="preserve">Data</t>
   </si>
   <si>
-    <t xml:space="preserve">Who have you bought data for? (multi-mentions possible)</t>
+    <t xml:space="preserve">Who prepaid data was purchased for?</t>
   </si>
   <si>
     <t xml:space="preserve">DataChannelEver</t>
   </si>
   <si>
-    <t xml:space="preserve">Where do you buy prepaid data - all purchases</t>
+    <t xml:space="preserve">All prepaid data purchase channels used</t>
   </si>
   <si>
     <t xml:space="preserve">DataChannelMain</t>
@@ -1646,13 +1649,13 @@
     <t xml:space="preserve">DataChannelAlso</t>
   </si>
   <si>
-    <t xml:space="preserve">Where else do you buy prepaid data - apart from the channel used most often?</t>
+    <t xml:space="preserve">Where else do you buy prepaid data?</t>
   </si>
   <si>
     <t xml:space="preserve">DataChannelOther</t>
   </si>
   <si>
-    <t xml:space="preserve">Where else have you bought prepaid data in the past 12 months?</t>
+    <t xml:space="preserve">Where else have you bought prepaid data in the past 12 months? (raw mentions)</t>
   </si>
   <si>
     <t xml:space="preserve">Lotto</t>
@@ -1979,16 +1982,13 @@
     <t xml:space="preserve">Bill</t>
   </si>
   <si>
-    <t xml:space="preserve">Who have you paid bills for? (multi-mentions possible)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASKED - self / other / none; covers all 14 bill categories</t>
+    <t xml:space="preserve">Who did you pay bills or accounts for in the last 12 months using a VAS method?</t>
   </si>
   <si>
     <t xml:space="preserve">BillChannelEver</t>
   </si>
   <si>
-    <t xml:space="preserve">Where do you pay bills - all spend</t>
+    <t xml:space="preserve">All bill payment channels used</t>
   </si>
   <si>
     <t xml:space="preserve">BillChannelMain</t>
@@ -2000,13 +2000,13 @@
     <t xml:space="preserve">BillChannelAlso</t>
   </si>
   <si>
-    <t xml:space="preserve">Where else do you pay bills - apart from the channel used most often?</t>
+    <t xml:space="preserve">Where else do you pay bills?</t>
   </si>
   <si>
     <t xml:space="preserve">BillChannelOther</t>
   </si>
   <si>
-    <t xml:space="preserve">Where else have you paid bills in the past 12 months?</t>
+    <t xml:space="preserve">Where else have you paid bills in the past 12 months? (raw mentions)</t>
   </si>
   <si>
     <t xml:space="preserve">Event</t>
@@ -2121,6 +2121,90 @@
   </si>
   <si>
     <t xml:space="preserve">Gambling transactions a month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillMunicipal_For</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who the municipal account was paid on behalf of?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillDSTV_For</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who was the DSTV / Multichoice account paid on behalf of?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillInternet_For</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who the internet subscription was paid on behalf of?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTelkom_For</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who was the Telkom or cellphone bill was paid on behalf of?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillInsurance_For</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who the insurance or funeral policy was paid on behalf of?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillVehicle_For</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who the vehicle licence was paid on behalf of?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTVLicence_For</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who the TV licence was paid on behalf of?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillRetail_For</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who the retail credit account was paid on behalf of?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillClothing_For</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who the clothing or fashion account was paid on behalf of?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillFurniture_For</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who the furniture account was paid on behalf of?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillEducation_For</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who education fees were paid on behalf of?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillHealth_For</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who health bills were paid on behalf of?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillTraffic_For</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who traffic fines were paid for?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BillOther_For</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who other bills were paid for?</t>
   </si>
 </sst>
 </file>
@@ -2128,19 +2212,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -2163,9 +2241,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2456,19 +2533,19 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="32.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="72.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="58.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="38.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="88.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="46.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2898,224 +2975,224 @@
         <v>83</v>
       </c>
       <c r="C40" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B41" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C41" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B42" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C42" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B43" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C43" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B44" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C44" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C45" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B46" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C46" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B47" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C47" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B48" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C48" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B49" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C49" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B50" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C50" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B51" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C51" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B52" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C52" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B53" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C53" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B54" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C54" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B55" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C55" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B56" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C56" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B57" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C57" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B58" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C58" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B59" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C59" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B60" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C60" t="s">
         <v>23</v>
@@ -3123,10 +3200,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B61" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C61" t="s">
         <v>23</v>
@@ -3134,10 +3211,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B62" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C62" t="s">
         <v>23</v>
@@ -3145,10 +3222,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B63" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C63" t="s">
         <v>23</v>
@@ -3156,10 +3233,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B64" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C64" t="s">
         <v>23</v>
@@ -3167,10 +3244,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B65" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C65" t="s">
         <v>23</v>
@@ -3178,10 +3255,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B66" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C66" t="s">
         <v>23</v>
@@ -3189,10 +3266,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B67" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C67" t="s">
         <v>23</v>
@@ -3200,10 +3277,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B68" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C68" t="s">
         <v>23</v>
@@ -3211,10 +3288,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B69" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C69" t="s">
         <v>23</v>
@@ -3222,10 +3299,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B70" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C70" t="s">
         <v>23</v>
@@ -3233,10 +3310,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B71" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C71" t="s">
         <v>23</v>
@@ -3244,10 +3321,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B72" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C72" t="s">
         <v>23</v>
@@ -3255,10 +3332,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B73" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C73" t="s">
         <v>23</v>
@@ -3266,10 +3343,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B74" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C74" t="s">
         <v>23</v>
@@ -3277,10 +3354,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B75" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C75" t="s">
         <v>23</v>
@@ -3288,10 +3365,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B76" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C76" t="s">
         <v>23</v>
@@ -3299,10 +3376,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B77" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C77" t="s">
         <v>23</v>
@@ -3310,10 +3387,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B78" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C78" t="s">
         <v>23</v>
@@ -3321,10 +3398,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B79" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C79" t="s">
         <v>23</v>
@@ -3332,10 +3409,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B80" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C80" t="s">
         <v>23</v>
@@ -3343,21 +3420,21 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B81" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C81" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B82" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C82" t="s">
         <v>23</v>
@@ -3365,10 +3442,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B83" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C83" t="s">
         <v>23</v>
@@ -3376,10 +3453,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B84" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C84" t="s">
         <v>23</v>
@@ -3387,10 +3464,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B85" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C85" t="s">
         <v>23</v>
@@ -3398,10 +3475,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B86" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C86" t="s">
         <v>23</v>
@@ -3409,10 +3486,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B87" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C87" t="s">
         <v>23</v>
@@ -3420,10 +3497,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B88" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C88" t="s">
         <v>23</v>
@@ -3431,10 +3508,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B89" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C89" t="s">
         <v>23</v>
@@ -3442,10 +3519,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B90" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C90" t="s">
         <v>23</v>
@@ -3453,10 +3530,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B91" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C91" t="s">
         <v>23</v>
@@ -3464,10 +3541,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B92" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C92" t="s">
         <v>23</v>
@@ -3475,10 +3552,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B93" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C93" t="s">
         <v>23</v>
@@ -3486,10 +3563,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B94" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C94" t="s">
         <v>23</v>
@@ -3497,10 +3574,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B95" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C95" t="s">
         <v>23</v>
@@ -3508,10 +3585,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B96" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C96" t="s">
         <v>23</v>
@@ -3519,10 +3596,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B97" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C97" t="s">
         <v>23</v>
@@ -3530,10 +3607,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B98" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C98" t="s">
         <v>23</v>
@@ -3541,10 +3618,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B99" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C99" t="s">
         <v>23</v>
@@ -3552,10 +3629,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B100" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C100" t="s">
         <v>23</v>
@@ -3563,10 +3640,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B101" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C101" t="s">
         <v>23</v>
@@ -3574,10 +3651,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B102" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C102" t="s">
         <v>23</v>
@@ -3585,10 +3662,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B103" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C103" t="s">
         <v>23</v>
@@ -3596,10 +3673,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B104" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C104" t="s">
         <v>23</v>
@@ -3607,10 +3684,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B105" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C105" t="s">
         <v>23</v>
@@ -3618,10 +3695,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B106" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C106" t="s">
         <v>23</v>
@@ -3629,10 +3706,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B107" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C107" t="s">
         <v>23</v>
@@ -3640,10 +3717,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B108" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C108" t="s">
         <v>23</v>
@@ -3651,10 +3728,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B109" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C109" t="s">
         <v>23</v>
@@ -3662,10 +3739,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B110" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C110" t="s">
         <v>23</v>
@@ -3673,10 +3750,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B111" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C111" t="s">
         <v>23</v>
@@ -3684,10 +3761,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B112" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C112" t="s">
         <v>23</v>
@@ -3695,10 +3772,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B113" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C113" t="s">
         <v>23</v>
@@ -3706,10 +3783,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B114" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C114" t="s">
         <v>23</v>
@@ -3717,10 +3794,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B115" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C115" t="s">
         <v>23</v>
@@ -3728,10 +3805,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B116" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C116" t="s">
         <v>23</v>
@@ -3739,10 +3816,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B117" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C117" t="s">
         <v>23</v>
@@ -3750,10 +3827,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B118" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C118" t="s">
         <v>23</v>
@@ -3761,10 +3838,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B119" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C119" t="s">
         <v>23</v>
@@ -3772,10 +3849,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B120" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C120" t="s">
         <v>23</v>
@@ -3783,10 +3860,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B121" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C121" t="s">
         <v>23</v>
@@ -3794,10 +3871,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B122" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C122" t="s">
         <v>23</v>
@@ -3805,10 +3882,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B123" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C123" t="s">
         <v>23</v>
@@ -3816,10 +3893,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B124" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C124" t="s">
         <v>23</v>
@@ -3827,10 +3904,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B125" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C125" t="s">
         <v>23</v>
@@ -3838,10 +3915,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B126" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C126" t="s">
         <v>23</v>
@@ -3849,10 +3926,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B127" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C127" t="s">
         <v>23</v>
@@ -3860,10 +3937,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B128" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C128" t="s">
         <v>23</v>
@@ -3871,10 +3948,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B129" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C129" t="s">
         <v>23</v>
@@ -3882,10 +3959,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B130" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C130" t="s">
         <v>23</v>
@@ -3893,10 +3970,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B131" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C131" t="s">
         <v>23</v>
@@ -3904,10 +3981,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B132" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C132" t="s">
         <v>23</v>
@@ -3915,10 +3992,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B133" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C133" t="s">
         <v>23</v>
@@ -3926,10 +4003,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B134" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C134" t="s">
         <v>23</v>
@@ -3937,10 +4014,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B135" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C135" t="s">
         <v>23</v>
@@ -3948,10 +4025,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B136" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C136" t="s">
         <v>23</v>
@@ -3959,10 +4036,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B137" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C137" t="s">
         <v>23</v>
@@ -3970,10 +4047,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B138" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C138" t="s">
         <v>23</v>
@@ -3981,10 +4058,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B139" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C139" t="s">
         <v>23</v>
@@ -3992,10 +4069,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B140" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C140" t="s">
         <v>23</v>
@@ -4003,10 +4080,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B141" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C141" t="s">
         <v>23</v>
@@ -4014,10 +4091,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B142" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C142" t="s">
         <v>23</v>
@@ -4025,10 +4102,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B143" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C143" t="s">
         <v>23</v>
@@ -4036,10 +4113,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B144" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C144" t="s">
         <v>23</v>
@@ -4047,10 +4124,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B145" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C145" t="s">
         <v>23</v>
@@ -4058,10 +4135,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B146" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C146" t="s">
         <v>23</v>
@@ -4069,10 +4146,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B147" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C147" t="s">
         <v>23</v>
@@ -4080,10 +4157,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B148" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C148" t="s">
         <v>23</v>
@@ -4091,10 +4168,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B149" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C149" t="s">
         <v>23</v>
@@ -4102,10 +4179,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B150" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C150" t="s">
         <v>23</v>
@@ -4113,10 +4190,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B151" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C151" t="s">
         <v>23</v>
@@ -4124,10 +4201,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B152" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C152" t="s">
         <v>23</v>
@@ -4135,10 +4212,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B153" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C153" t="s">
         <v>23</v>
@@ -4146,10 +4223,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B154" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C154" t="s">
         <v>23</v>
@@ -4157,10 +4234,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B155" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C155" t="s">
         <v>23</v>
@@ -4168,10 +4245,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B156" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C156" t="s">
         <v>23</v>
@@ -4179,10 +4256,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B157" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C157" t="s">
         <v>23</v>
@@ -4190,10 +4267,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B158" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C158" t="s">
         <v>23</v>
@@ -4201,10 +4278,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B159" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C159" t="s">
         <v>23</v>
@@ -4212,10 +4289,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B160" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C160" t="s">
         <v>23</v>
@@ -4223,10 +4300,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B161" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C161" t="s">
         <v>23</v>
@@ -4234,10 +4311,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B162" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C162" t="s">
         <v>23</v>
@@ -4245,10 +4322,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B163" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C163" t="s">
         <v>23</v>
@@ -4256,10 +4333,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B164" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C164" t="s">
         <v>23</v>
@@ -4267,10 +4344,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B165" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C165" t="s">
         <v>23</v>
@@ -4278,10 +4355,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B166" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C166" t="s">
         <v>23</v>
@@ -4289,10 +4366,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B167" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C167" t="s">
         <v>23</v>
@@ -4300,10 +4377,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B168" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C168" t="s">
         <v>23</v>
@@ -4311,10 +4388,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B169" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C169" t="s">
         <v>23</v>
@@ -4322,10 +4399,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B170" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C170" t="s">
         <v>23</v>
@@ -4333,10 +4410,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B171" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C171" t="s">
         <v>23</v>
@@ -4344,10 +4421,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B172" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C172" t="s">
         <v>23</v>
@@ -4355,10 +4432,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B173" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C173" t="s">
         <v>23</v>
@@ -4366,10 +4443,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B174" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C174" t="s">
         <v>23</v>
@@ -4377,10 +4454,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B175" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C175" t="s">
         <v>23</v>
@@ -4388,10 +4465,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B176" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C176" t="s">
         <v>23</v>
@@ -4399,10 +4476,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B177" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C177" t="s">
         <v>23</v>
@@ -4410,10 +4487,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B178" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C178" t="s">
         <v>23</v>
@@ -4421,10 +4498,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B179" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C179" t="s">
         <v>23</v>
@@ -4432,10 +4509,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B180" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C180" t="s">
         <v>23</v>
@@ -4443,10 +4520,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B181" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C181" t="s">
         <v>23</v>
@@ -4454,10 +4531,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B182" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C182" t="s">
         <v>23</v>
@@ -4465,10 +4542,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B183" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C183" t="s">
         <v>23</v>
@@ -4476,10 +4553,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B184" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C184" t="s">
         <v>23</v>
@@ -4487,10 +4564,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B185" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C185" t="s">
         <v>23</v>
@@ -4498,10 +4575,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B186" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C186" t="s">
         <v>23</v>
@@ -4509,10 +4586,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B187" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C187" t="s">
         <v>23</v>
@@ -4520,10 +4597,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B188" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C188" t="s">
         <v>23</v>
@@ -4531,10 +4608,10 @@
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B189" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C189" t="s">
         <v>23</v>
@@ -4542,10 +4619,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B190" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C190" t="s">
         <v>23</v>
@@ -4553,10 +4630,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B191" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C191" t="s">
         <v>23</v>
@@ -4564,10 +4641,10 @@
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B192" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C192" t="s">
         <v>23</v>
@@ -4575,10 +4652,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B193" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C193" t="s">
         <v>23</v>
@@ -4586,10 +4663,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B194" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C194" t="s">
         <v>23</v>
@@ -4597,10 +4674,10 @@
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B195" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C195" t="s">
         <v>23</v>
@@ -4608,10 +4685,10 @@
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B196" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C196" t="s">
         <v>23</v>
@@ -4619,10 +4696,10 @@
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B197" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C197" t="s">
         <v>23</v>
@@ -4630,10 +4707,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B198" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C198" t="s">
         <v>23</v>
@@ -4641,10 +4718,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B199" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C199" t="s">
         <v>23</v>
@@ -4652,1355 +4729,1355 @@
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B200" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C200" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B201" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C201" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B202" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C202" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B203" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C203" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B204" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C204" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B205" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C205" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B206" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C206" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B207" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C207" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B208" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C208" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B209" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C209" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B210" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C210" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B211" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C211" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B212" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C212" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B213" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C213" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B214" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C214" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B215" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C215" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B216" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C216" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B217" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C217" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B218" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C218" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B219" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C219" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B220" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C220" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B221" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C221" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B222" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C222" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B223" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C223" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B224" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C224" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B225" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C225" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B226" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C226" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B227" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C227" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B228" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C228" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B229" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C229" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B230" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C230" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B231" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C231" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B232" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C232" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B233" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C233" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B234" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C234" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B235" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C235" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B236" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C236" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B237" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C237" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B238" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C238" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B239" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C239" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B240" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C240" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B241" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C241" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B242" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C242" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B243" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C243" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B244" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C244" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B245" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C245" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B246" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C246" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B247" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C247" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B248" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C248" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B249" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C249" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B250" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C250" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B251" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C251" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B252" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C252" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B253" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C253" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B254" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C254" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B255" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C255" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B256" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C256" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B257" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C257" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B258" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C258" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B259" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C259" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B260" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C260" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B261" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C261" t="s">
-        <v>516</v>
+        <v>23</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B262" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C262" t="s">
-        <v>519</v>
+        <v>23</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B263" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C263" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B264" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C264" t="s">
-        <v>519</v>
+        <v>23</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B265" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C265" t="s">
-        <v>522</v>
+        <v>23</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B266" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C266" t="s">
-        <v>516</v>
+        <v>23</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B267" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C267" t="s">
-        <v>519</v>
+        <v>23</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B268" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C268" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B269" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C269" t="s">
-        <v>519</v>
+        <v>23</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B270" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C270" t="s">
-        <v>522</v>
+        <v>23</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B271" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C271" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B272" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C272" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B273" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C273" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B274" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C274" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B275" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C275" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B276" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C276" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B277" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C277" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B278" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C278" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B279" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C279" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B280" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C280" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B281" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C281" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="s">
+        <v>572</v>
+      </c>
+      <c r="B282" t="s">
+        <v>573</v>
+      </c>
+      <c r="C282" t="s">
         <v>571</v>
-      </c>
-      <c r="B282" t="s">
-        <v>572</v>
-      </c>
-      <c r="C282" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B283" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C283" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B284" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C284" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B285" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C285" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B286" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C286" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B287" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C287" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B288" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C288" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B289" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C289" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B290" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C290" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B291" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C291" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B292" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C292" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B293" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C293" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B294" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C294" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B295" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C295" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B296" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C296" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B297" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C297" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B298" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C298" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B299" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C299" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B300" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C300" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B301" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C301" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B302" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C302" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B303" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C303" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B304" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C304" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B305" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C305" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B306" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C306" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B307" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C307" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B308" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C308" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B309" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C309" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B310" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C310" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B311" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C311" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B312" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C312" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B313" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C313" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B314" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C314" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B315" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C315" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B316" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C316" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B317" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C317" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B318" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C318" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B319" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C319" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B320" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C320" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B321" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C321" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B322" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C322" t="s">
-        <v>656</v>
+        <v>23</v>
       </c>
     </row>
     <row r="323">
@@ -6011,7 +6088,7 @@
         <v>658</v>
       </c>
       <c r="C323" t="s">
-        <v>519</v>
+        <v>23</v>
       </c>
     </row>
     <row r="324">
@@ -6022,7 +6099,7 @@
         <v>660</v>
       </c>
       <c r="C324" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="325">
@@ -6033,7 +6110,7 @@
         <v>662</v>
       </c>
       <c r="C325" t="s">
-        <v>519</v>
+        <v>23</v>
       </c>
     </row>
     <row r="326">
@@ -6044,7 +6121,7 @@
         <v>664</v>
       </c>
       <c r="C326" t="s">
-        <v>522</v>
+        <v>23</v>
       </c>
     </row>
     <row r="327">
@@ -6066,7 +6143,7 @@
         <v>669</v>
       </c>
       <c r="C328" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="329">
@@ -6077,7 +6154,7 @@
         <v>671</v>
       </c>
       <c r="C329" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="330">
@@ -6088,7 +6165,7 @@
         <v>673</v>
       </c>
       <c r="C330" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="331">
@@ -6099,7 +6176,7 @@
         <v>675</v>
       </c>
       <c r="C331" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="332">
@@ -6110,7 +6187,7 @@
         <v>677</v>
       </c>
       <c r="C332" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="333">
@@ -6232,6 +6309,160 @@
       </c>
       <c r="C343" t="s">
         <v>692</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="s">
+        <v>703</v>
+      </c>
+      <c r="B344" t="s">
+        <v>704</v>
+      </c>
+      <c r="C344" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="s">
+        <v>705</v>
+      </c>
+      <c r="B345" t="s">
+        <v>706</v>
+      </c>
+      <c r="C345" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="s">
+        <v>707</v>
+      </c>
+      <c r="B346" t="s">
+        <v>708</v>
+      </c>
+      <c r="C346" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="s">
+        <v>709</v>
+      </c>
+      <c r="B347" t="s">
+        <v>710</v>
+      </c>
+      <c r="C347" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="s">
+        <v>711</v>
+      </c>
+      <c r="B348" t="s">
+        <v>712</v>
+      </c>
+      <c r="C348" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="s">
+        <v>713</v>
+      </c>
+      <c r="B349" t="s">
+        <v>714</v>
+      </c>
+      <c r="C349" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="s">
+        <v>715</v>
+      </c>
+      <c r="B350" t="s">
+        <v>716</v>
+      </c>
+      <c r="C350" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="s">
+        <v>717</v>
+      </c>
+      <c r="B351" t="s">
+        <v>718</v>
+      </c>
+      <c r="C351" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="s">
+        <v>719</v>
+      </c>
+      <c r="B352" t="s">
+        <v>720</v>
+      </c>
+      <c r="C352" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="s">
+        <v>721</v>
+      </c>
+      <c r="B353" t="s">
+        <v>722</v>
+      </c>
+      <c r="C353" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="s">
+        <v>723</v>
+      </c>
+      <c r="B354" t="s">
+        <v>724</v>
+      </c>
+      <c r="C354" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="s">
+        <v>725</v>
+      </c>
+      <c r="B355" t="s">
+        <v>726</v>
+      </c>
+      <c r="C355" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="s">
+        <v>727</v>
+      </c>
+      <c r="B356" t="s">
+        <v>728</v>
+      </c>
+      <c r="C356" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="s">
+        <v>729</v>
+      </c>
+      <c r="B357" t="s">
+        <v>730</v>
+      </c>
+      <c r="C357" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
